--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,17 +67,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="9"/>
@@ -88,7 +77,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -98,11 +87,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -128,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,28 +133,13 @@
     <xf numFmtId="4" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -626,23 +595,23 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>T-01A</t>
+          <t>T-13C</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>109.74</v>
+        <v>54.2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>5134</v>
+        <v>2992</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>6695</v>
+        <v>20464</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4138</v>
+        <v>19016</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3555</v>
+        <v>11982</v>
       </c>
       <c r="G5" s="8">
         <f>D5/1000</f>
@@ -661,23 +630,23 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>T-11B</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>114.01</v>
+        <v>46.69</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>5071</v>
+        <v>3078</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>6405</v>
+        <v>20181</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>3949</v>
+        <v>18905</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>2084</v>
+        <v>11323</v>
       </c>
       <c r="G6" s="15">
         <f>D6/1000</f>
@@ -694,95 +663,95 @@
       <c r="J6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>T-07C</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>54.78</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>3399</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>6351</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>4680</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>2115</v>
-      </c>
-      <c r="G7" s="15">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>T-13D</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3161</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>19770</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>18214</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>11726</v>
+      </c>
+      <c r="G7" s="8">
         <f>D7/1000</f>
         <v/>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="8">
         <f>E7/1000</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="9">
         <f>IFERROR(D7/F7,"")</f>
         <v/>
       </c>
-      <c r="J7" s="17" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>T-09B</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="n">
-        <v>51.45</v>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>3530</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>6232</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>4529</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>2736</v>
-      </c>
-      <c r="G8" s="22">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>T-13B</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>3110</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>19740</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>18228</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>11159</v>
+      </c>
+      <c r="G8" s="15">
         <f>D8/1000</f>
         <v/>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="15">
         <f>E8/1000</f>
         <v/>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="16">
         <f>IFERROR(D8/F8,"")</f>
         <v/>
       </c>
-      <c r="J8" s="24" t="inlineStr"/>
+      <c r="J8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>T-03A</t>
+          <t>T-11C</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>108.06</v>
+        <v>52.01</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5283</v>
+        <v>3100</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5885</v>
+        <v>19716</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3953</v>
+        <v>18190</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>2445</v>
+        <v>10871</v>
       </c>
       <c r="G9" s="8">
         <f>D9/1000</f>
@@ -799,60 +768,60 @@
       <c r="J9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>T-07B</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="n">
-        <v>63.94</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>3736</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>5881</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>4329</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>2244</v>
-      </c>
-      <c r="G10" s="22">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>T-11A</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>3271</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>19672</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>18208</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>11475</v>
+      </c>
+      <c r="G10" s="15">
         <f>D10/1000</f>
         <v/>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="15">
         <f>E10/1000</f>
         <v/>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="16">
         <f>IFERROR(D10/F10,"")</f>
         <v/>
       </c>
-      <c r="J10" s="24" t="inlineStr"/>
+      <c r="J10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>T-12A</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>110.23</v>
+        <v>263.78</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5065</v>
+        <v>6934</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>5740</v>
+        <v>19151</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3218</v>
+        <v>15815</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>2669</v>
+        <v>9384</v>
       </c>
       <c r="G11" s="8">
         <f>D11/1000</f>
@@ -869,95 +838,95 @@
       <c r="J11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>T-09A</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>3147</v>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>5597</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>4041</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>2720</v>
-      </c>
-      <c r="G12" s="22">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>T-11D</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>3481</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>19053</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>17474</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>10886</v>
+      </c>
+      <c r="G12" s="15">
         <f>D12/1000</f>
         <v/>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="15">
         <f>E12/1000</f>
         <v/>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="16">
         <f>IFERROR(D12/F12,"")</f>
         <v/>
       </c>
-      <c r="J12" s="24" t="inlineStr"/>
+      <c r="J12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>T-01C</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>114.58</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>5085</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>5389</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>2983</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>1346</v>
-      </c>
-      <c r="G13" s="15">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>T-13A</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>53.65</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3197</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>18998</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>17624</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>11107</v>
+      </c>
+      <c r="G13" s="8">
         <f>D13/1000</f>
         <v/>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="8">
         <f>E13/1000</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="9">
         <f>IFERROR(D13/F13,"")</f>
         <v/>
       </c>
-      <c r="J13" s="17" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>T-07D</t>
+          <t>T-10A</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>43.25</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>3108</v>
+        <v>4140</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>5336</v>
+        <v>18466</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>3804</v>
+        <v>16421</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1623</v>
+        <v>10009</v>
       </c>
       <c r="G14" s="15">
         <f>D14/1000</f>
@@ -976,23 +945,23 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>T-07A</t>
+          <t>T-14A</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>50.64</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>3002</v>
+        <v>4640</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>4917</v>
+        <v>16735</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3633</v>
+        <v>14456</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1983</v>
+        <v>8248</v>
       </c>
       <c r="G15" s="8">
         <f>D15/1000</f>
@@ -1011,23 +980,23 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>T-03B</t>
+          <t>T-14D</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>113.04</v>
+        <v>96.37</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>5041</v>
+        <v>4536</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>4810</v>
+        <v>16730</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2998</v>
+        <v>14471</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>1508</v>
+        <v>8256</v>
       </c>
       <c r="G16" s="15">
         <f>D16/1000</f>
@@ -1044,60 +1013,60 @@
       <c r="J16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>T-02</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>210.74</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>9468</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>4707</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>1223</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>976</v>
-      </c>
-      <c r="G17" s="15">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>T-15B</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>5499</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>16283</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>14217</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>8307</v>
+      </c>
+      <c r="G17" s="8">
         <f>D17/1000</f>
         <v/>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="8">
         <f>E17/1000</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="9">
         <f>IFERROR(D17/F17,"")</f>
         <v/>
       </c>
-      <c r="J17" s="17" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>T-06D</t>
+          <t>T-05</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>148.91</v>
+        <v>114.01</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>5858</v>
+        <v>5071</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>4359</v>
+        <v>15153</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>2016</v>
+        <v>12712</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>617</v>
+        <v>9352</v>
       </c>
       <c r="G18" s="15">
         <f>D18/1000</f>
@@ -1114,60 +1083,60 @@
       <c r="J18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>T-06E</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>264.72</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>6929</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>4353</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>986</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>399</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>T-07C</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>3399</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>15117</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>13471</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>9205</v>
+      </c>
+      <c r="G19" s="8">
         <f>D19/1000</f>
         <v/>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="8">
         <f>E19/1000</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="9">
         <f>IFERROR(D19/F19,"")</f>
         <v/>
       </c>
-      <c r="J19" s="17" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>T-06B</t>
+          <t>T-15C</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>73.88</v>
+        <v>95.86</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>4134</v>
+        <v>4455</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>4319</v>
+        <v>15107</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>2888</v>
+        <v>12892</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1134</v>
+        <v>7221</v>
       </c>
       <c r="G20" s="15">
         <f>D20/1000</f>
@@ -1186,23 +1155,23 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>T-08A</t>
+          <t>T-09B</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>14.18</v>
+        <v>51.45</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1756</v>
+        <v>3530</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3961</v>
+        <v>15023</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>3089</v>
+        <v>13321</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>1985</v>
+        <v>9210</v>
       </c>
       <c r="G21" s="8">
         <f>D21/1000</f>
@@ -1221,23 +1190,23 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>T-06C</t>
+          <t>T-07B</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>31.74</v>
+        <v>63.94</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>2739</v>
+        <v>3736</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>3951</v>
+        <v>14672</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>2588</v>
+        <v>13120</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>826</v>
+        <v>9056</v>
       </c>
       <c r="G22" s="15">
         <f>D22/1000</f>
@@ -1254,60 +1223,60 @@
       <c r="J22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>T-04A</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>100.42</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>5093</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>3851</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>2036</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>615</v>
-      </c>
-      <c r="G23" s="15">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>T-09A</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>51.15</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>3147</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>14388</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>12832</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>8842</v>
+      </c>
+      <c r="G23" s="8">
         <f>D23/1000</f>
         <v/>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="8">
         <f>E23/1000</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="9">
         <f>IFERROR(D23/F23,"")</f>
         <v/>
       </c>
-      <c r="J23" s="17" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>T-04B</t>
+          <t>T-01C</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>51.93</v>
+        <v>114.58</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>3411</v>
+        <v>5085</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>3716</v>
+        <v>14152</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>2033</v>
+        <v>11745</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>632</v>
+        <v>8501</v>
       </c>
       <c r="G24" s="15">
         <f>D24/1000</f>
@@ -1324,709 +1293,555 @@
       <c r="J24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>T-04</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n">
-        <v>107.45</v>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>5565</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>2864</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>97</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>96</v>
-      </c>
-      <c r="G25" s="15">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>T-07D</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>3108</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>14108</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>12595</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>8461</v>
+      </c>
+      <c r="G25" s="8">
         <f>D25/1000</f>
         <v/>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="8">
         <f>E25/1000</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="9">
         <f>IFERROR(D25/F25,"")</f>
         <v/>
       </c>
-      <c r="J25" s="17" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>T-10A</t>
+          <t>T-03A</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>67.81999999999999</v>
+        <v>108.06</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>4140</v>
-      </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>5283</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>14094</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>11784</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>6205</v>
-      </c>
-      <c r="G26" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H26" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>9732</v>
+      </c>
+      <c r="G26" s="15">
+        <f>D26/1000</f>
+        <v/>
+      </c>
+      <c r="H26" s="15">
+        <f>E26/1000</f>
+        <v/>
+      </c>
+      <c r="I26" s="16">
+        <f>IFERROR(D26/F26,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="17" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>T-11A</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n">
-        <v>61.24</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>3271</v>
-      </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>6767</v>
-      </c>
-      <c r="G27" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>T-01A</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>109.74</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>5134</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>13766</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>11788</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>10367</v>
+      </c>
+      <c r="G27" s="8">
+        <f>D27/1000</f>
+        <v/>
+      </c>
+      <c r="H27" s="8">
+        <f>E27/1000</f>
+        <v/>
+      </c>
+      <c r="I27" s="9">
+        <f>IFERROR(D27/F27,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>T-11B</t>
+          <t>T-07A</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>46.69</v>
+        <v>50.64</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>3078</v>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>3002</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>13708</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>12426</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>5995</v>
-      </c>
-      <c r="G28" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>8442</v>
+      </c>
+      <c r="G28" s="15">
+        <f>D28/1000</f>
+        <v/>
+      </c>
+      <c r="H28" s="15">
+        <f>E28/1000</f>
+        <v/>
+      </c>
+      <c r="I28" s="16">
+        <f>IFERROR(D28/F28,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>T-11C</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="n">
-        <v>52.01</v>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>5662</v>
-      </c>
-      <c r="G29" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>T-06D</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>148.91</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>5858</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>13105</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>10780</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>7712</v>
+      </c>
+      <c r="G29" s="8">
+        <f>D29/1000</f>
+        <v/>
+      </c>
+      <c r="H29" s="8">
+        <f>E29/1000</f>
+        <v/>
+      </c>
+      <c r="I29" s="9">
+        <f>IFERROR(D29/F29,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>T-11D</t>
+          <t>T-06E</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>70.47</v>
+        <v>264.72</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>3481</v>
-      </c>
-      <c r="D30" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>6929</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>13103</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>9805</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>6319</v>
-      </c>
-      <c r="G30" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>6957</v>
+      </c>
+      <c r="G30" s="15">
+        <f>D30/1000</f>
+        <v/>
+      </c>
+      <c r="H30" s="15">
+        <f>E30/1000</f>
+        <v/>
+      </c>
+      <c r="I30" s="16">
+        <f>IFERROR(D30/F30,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>T-12A</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="n">
-        <v>263.78</v>
-      </c>
-      <c r="C31" s="13" t="n">
-        <v>6934</v>
-      </c>
-      <c r="D31" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>6449</v>
-      </c>
-      <c r="G31" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>T-06B</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>4134</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>13096</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>11681</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>7712</v>
+      </c>
+      <c r="G31" s="8">
+        <f>D31/1000</f>
+        <v/>
+      </c>
+      <c r="H31" s="8">
+        <f>E31/1000</f>
+        <v/>
+      </c>
+      <c r="I31" s="9">
+        <f>IFERROR(D31/F31,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>T-13A</t>
+          <t>T-03B</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>53.65</v>
+        <v>113.04</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>3197</v>
-      </c>
-      <c r="D32" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>5041</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>13024</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>10827</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>7258</v>
-      </c>
-      <c r="G32" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>8850</v>
+      </c>
+      <c r="G32" s="15">
+        <f>D32/1000</f>
+        <v/>
+      </c>
+      <c r="H32" s="15">
+        <f>E32/1000</f>
+        <v/>
+      </c>
+      <c r="I32" s="16">
+        <f>IFERROR(D32/F32,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="17" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>T-13B</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>3110</v>
-      </c>
-      <c r="D33" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>7804</v>
-      </c>
-      <c r="G33" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>T-01</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>110.23</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>5065</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>12784</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>10868</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>9477</v>
+      </c>
+      <c r="G33" s="8">
+        <f>D33/1000</f>
+        <v/>
+      </c>
+      <c r="H33" s="8">
+        <f>E33/1000</f>
+        <v/>
+      </c>
+      <c r="I33" s="9">
+        <f>IFERROR(D33/F33,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>T-13C</t>
+          <t>T-08A</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>54.2</v>
+        <v>14.18</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>2992</v>
-      </c>
-      <c r="D34" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>1756</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>12754</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>11882</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>8271</v>
-      </c>
-      <c r="G34" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J34" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>7912</v>
+      </c>
+      <c r="G34" s="15">
+        <f>D34/1000</f>
+        <v/>
+      </c>
+      <c r="H34" s="15">
+        <f>E34/1000</f>
+        <v/>
+      </c>
+      <c r="I34" s="16">
+        <f>IFERROR(D34/F34,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>T-13D</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="n">
-        <v>61.56</v>
-      </c>
-      <c r="C35" s="13" t="n">
-        <v>3161</v>
-      </c>
-      <c r="D35" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>7589</v>
-      </c>
-      <c r="G35" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J35" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>T-06C</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>2739</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>12715</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>11352</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>7775</v>
+      </c>
+      <c r="G35" s="8">
+        <f>D35/1000</f>
+        <v/>
+      </c>
+      <c r="H35" s="8">
+        <f>E35/1000</f>
+        <v/>
+      </c>
+      <c r="I35" s="9">
+        <f>IFERROR(D35/F35,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>T-14A</t>
+          <t>T-04A</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>99.15000000000001</v>
+        <v>100.42</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>4640</v>
-      </c>
-      <c r="D36" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E36" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>5093</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>12054</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>9975</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>5179</v>
-      </c>
-      <c r="G36" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>7977</v>
+      </c>
+      <c r="G36" s="15">
+        <f>D36/1000</f>
+        <v/>
+      </c>
+      <c r="H36" s="15">
+        <f>E36/1000</f>
+        <v/>
+      </c>
+      <c r="I36" s="16">
+        <f>IFERROR(D36/F36,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="17" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>T-14D</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n">
-        <v>96.37</v>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>4536</v>
-      </c>
-      <c r="D37" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>5221</v>
-      </c>
-      <c r="G37" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>T-04B</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>3411</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>12053</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>10771</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>7991</v>
+      </c>
+      <c r="G37" s="8">
+        <f>D37/1000</f>
+        <v/>
+      </c>
+      <c r="H37" s="8">
+        <f>E37/1000</f>
+        <v/>
+      </c>
+      <c r="I37" s="9">
+        <f>IFERROR(D37/F37,"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>T-15B</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>143</v>
+        <v>210.74</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>5499</v>
-      </c>
-      <c r="D38" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E38" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>9468</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>11735</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>8876</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3994</v>
-      </c>
-      <c r="G38" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>7561</v>
+      </c>
+      <c r="G38" s="15">
+        <f>D38/1000</f>
+        <v/>
+      </c>
+      <c r="H38" s="15">
+        <f>E38/1000</f>
+        <v/>
+      </c>
+      <c r="I38" s="16">
+        <f>IFERROR(D38/F38,"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>T-15C</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="n">
-        <v>95.86</v>
-      </c>
-      <c r="C39" s="13" t="n">
-        <v>4455</v>
-      </c>
-      <c r="D39" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>3761</v>
-      </c>
-      <c r="G39" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J39" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>T-04</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>5565</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>11069</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>8542</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>7077</v>
+      </c>
+      <c r="G39" s="8">
+        <f>D39/1000</f>
+        <v/>
+      </c>
+      <c r="H39" s="8">
+        <f>E39/1000</f>
+        <v/>
+      </c>
+      <c r="I39" s="9">
+        <f>IFERROR(D39/F39,"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>TOTAL / MÁXIMO</t>
         </is>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="19">
         <f>SUM(B5:B39)</f>
         <v/>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="20">
         <f>MAX(IFERROR(D5:D39*1,0))</f>
         <v/>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="21">
         <f>IFERROR(MAX(G5:G39),"")</f>
         <v/>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="22">
         <f>IFERROR(AVERAGE(I5:I39),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>Fundo amarelo = precisa de conferência: fator ≥ 3,0, ligação suposta, ou talhão sem estrada. Veja a coluna Observação.</t>
         </is>
@@ -2051,127 +1866,127 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Como estes números foram calculados</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
       </c>
-      <c r="B3" s="37" t="inlineStr">
-        <is>
-          <t>Ponto de sede do projeto do Google Earth (-13.551609, -57.613586).</t>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Ponto de sede do projeto do Google Earth (-13.586393, -57.555499).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Talhões</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>35 polígonos da pasta FAZENDA JAVA.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Malha de estradas</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Divisas dos talhões (os carreadores correm nas divisas), costuradas onde talhões vizinhos são separados pela faixa do carreador (até 45 m), mais as estradas de dados/estradas_extra.json.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Dist. máxima</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Menor caminho pela estrada, da sede até o ponto MAIS EXTREMO do perímetro do talhão. Não corta por dentro da lavoura.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Dist. mínima</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Menor caminho pela estrada, da sede até o ponto de acesso mais próximo.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Linha reta</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Distância em linha reta da sede até a borda do talhão. Só referência.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Fator</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Dist. máxima ÷ linha reta. Fator alto = rota indireta, ou estrada faltando na malha.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Coordenadas</t>
         </is>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>SIRGAS 2000 / UTM 21S (EPSG:31981) para distâncias e áreas.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Resolução</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Malha densificada a cada 25 m — é a precisão do 'ponto mais extremo'.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Validação</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>A malha precisa ser conferida por quem roda a fazenda. Use o arquivo _bancada.html.</t>
         </is>

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -605,10 +605,10 @@
         <v>2992</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>20464</v>
+        <v>22832</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19016</v>
+        <v>20559</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>11982</v>
@@ -640,10 +640,10 @@
         <v>3078</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>20181</v>
+        <v>22513</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>18905</v>
+        <v>20789</v>
       </c>
       <c r="F6" s="14" t="n">
         <v>11323</v>
@@ -665,23 +665,23 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>T-13D</t>
+          <t>T-13B</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>61.56</v>
+        <v>58.52</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3161</v>
+        <v>3110</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>19770</v>
+        <v>22035</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>18214</v>
+        <v>19778</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>11726</v>
+        <v>11159</v>
       </c>
       <c r="G7" s="8">
         <f>D7/1000</f>
@@ -700,23 +700,23 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>T-13B</t>
+          <t>T-11C</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>58.52</v>
+        <v>52.01</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>3110</v>
+        <v>3100</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>19740</v>
+        <v>21572</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>18228</v>
+        <v>19720</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>11159</v>
+        <v>10871</v>
       </c>
       <c r="G8" s="15">
         <f>D8/1000</f>
@@ -735,23 +735,23 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>T-11C</t>
+          <t>T-11A</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>52.01</v>
+        <v>61.24</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>3100</v>
+        <v>3271</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>19716</v>
+        <v>21501</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>18190</v>
+        <v>19744</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>10871</v>
+        <v>11475</v>
       </c>
       <c r="G9" s="8">
         <f>D9/1000</f>
@@ -770,23 +770,23 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>T-11A</t>
+          <t>T-13D</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>61.24</v>
+        <v>61.56</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>3271</v>
+        <v>3161</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>19672</v>
+        <v>21492</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>18208</v>
+        <v>19741</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>11475</v>
+        <v>11726</v>
       </c>
       <c r="G10" s="15">
         <f>D10/1000</f>
@@ -815,10 +815,10 @@
         <v>6934</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>19151</v>
+        <v>21136</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>15815</v>
+        <v>17351</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>9384</v>
@@ -850,10 +850,10 @@
         <v>3481</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>19053</v>
+        <v>20914</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>17474</v>
+        <v>19004</v>
       </c>
       <c r="F12" s="14" t="n">
         <v>10886</v>
@@ -885,10 +885,10 @@
         <v>3197</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>18998</v>
+        <v>20654</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>17624</v>
+        <v>19164</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>11107</v>
@@ -920,10 +920,10 @@
         <v>4140</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>18466</v>
+        <v>20172</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>16421</v>
+        <v>17948</v>
       </c>
       <c r="F14" s="14" t="n">
         <v>10009</v>
@@ -945,23 +945,23 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>T-14A</t>
+          <t>T-15B</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>99.15000000000001</v>
+        <v>143</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>4640</v>
+        <v>5499</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>16735</v>
+        <v>18524</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>14456</v>
+        <v>15744</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>8248</v>
+        <v>8307</v>
       </c>
       <c r="G15" s="8">
         <f>D15/1000</f>
@@ -980,23 +980,23 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>T-14D</t>
+          <t>T-14A</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>96.37</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4536</v>
+        <v>4640</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>16730</v>
+        <v>18445</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>14471</v>
+        <v>15999</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>8256</v>
+        <v>8248</v>
       </c>
       <c r="G16" s="15">
         <f>D16/1000</f>
@@ -1015,23 +1015,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>T-15B</t>
+          <t>T-14D</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>143</v>
+        <v>96.37</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>5499</v>
+        <v>4536</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>16283</v>
+        <v>18432</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>14217</v>
+        <v>15999</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>8307</v>
+        <v>8256</v>
       </c>
       <c r="G17" s="8">
         <f>D17/1000</f>
@@ -1060,10 +1060,10 @@
         <v>5071</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>15153</v>
+        <v>17235</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>12712</v>
+        <v>14274</v>
       </c>
       <c r="F18" s="14" t="n">
         <v>9352</v>
@@ -1095,10 +1095,10 @@
         <v>3399</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>15117</v>
+        <v>17086</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>13471</v>
+        <v>15630</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>9205</v>
@@ -1130,10 +1130,10 @@
         <v>4455</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>15107</v>
+        <v>17081</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>12892</v>
+        <v>14419</v>
       </c>
       <c r="F20" s="14" t="n">
         <v>7221</v>
@@ -1155,23 +1155,23 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>T-09B</t>
+          <t>T-07B</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>51.45</v>
+        <v>63.94</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>3530</v>
+        <v>3736</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>15023</v>
+        <v>16810</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>13321</v>
+        <v>14652</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>9210</v>
+        <v>9056</v>
       </c>
       <c r="G21" s="8">
         <f>D21/1000</f>
@@ -1190,23 +1190,23 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>T-07B</t>
+          <t>T-09B</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>63.94</v>
+        <v>51.45</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>3736</v>
+        <v>3530</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>14672</v>
+        <v>16610</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>13120</v>
+        <v>14853</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>9056</v>
+        <v>9210</v>
       </c>
       <c r="G22" s="15">
         <f>D22/1000</f>
@@ -1225,23 +1225,23 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>T-09A</t>
+          <t>T-01C</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>51.15</v>
+        <v>114.58</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>3147</v>
+        <v>5085</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>14388</v>
+        <v>16199</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>12832</v>
+        <v>13286</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>8842</v>
+        <v>8501</v>
       </c>
       <c r="G23" s="8">
         <f>D23/1000</f>
@@ -1260,23 +1260,23 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>T-01C</t>
+          <t>T-07D</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>114.58</v>
+        <v>43.25</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>5085</v>
+        <v>3108</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>14152</v>
+        <v>16100</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>11745</v>
+        <v>14138</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>8501</v>
+        <v>8461</v>
       </c>
       <c r="G24" s="15">
         <f>D24/1000</f>
@@ -1295,23 +1295,23 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>T-07D</t>
+          <t>T-09A</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>43.25</v>
+        <v>51.15</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>3108</v>
+        <v>3147</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>14108</v>
+        <v>16023</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>12595</v>
+        <v>14369</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>8461</v>
+        <v>8842</v>
       </c>
       <c r="G25" s="8">
         <f>D25/1000</f>
@@ -1340,10 +1340,10 @@
         <v>5283</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>14094</v>
+        <v>15914</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>11784</v>
+        <v>13324</v>
       </c>
       <c r="F26" s="14" t="n">
         <v>9732</v>
@@ -1375,10 +1375,10 @@
         <v>5134</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>13766</v>
+        <v>15701</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>11788</v>
+        <v>13328</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>10367</v>
@@ -1410,10 +1410,10 @@
         <v>3002</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>13708</v>
+        <v>15673</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>12426</v>
+        <v>13963</v>
       </c>
       <c r="F28" s="14" t="n">
         <v>8442</v>
@@ -1435,23 +1435,23 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>T-06D</t>
+          <t>T-06C</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>148.91</v>
+        <v>31.74</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>5858</v>
+        <v>2739</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>13105</v>
+        <v>15008</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>10780</v>
+        <v>12891</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>7712</v>
+        <v>7775</v>
       </c>
       <c r="G29" s="8">
         <f>D29/1000</f>
@@ -1470,23 +1470,23 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>T-06E</t>
+          <t>T-06B</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>264.72</v>
+        <v>73.88</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>6929</v>
+        <v>4134</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>13103</v>
+        <v>14900</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>9805</v>
+        <v>13211</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>6957</v>
+        <v>7712</v>
       </c>
       <c r="G30" s="15">
         <f>D30/1000</f>
@@ -1505,20 +1505,20 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>T-06B</t>
+          <t>T-06D</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>73.88</v>
+        <v>148.91</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>4134</v>
+        <v>5858</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>13096</v>
+        <v>14788</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>11681</v>
+        <v>12319</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>7712</v>
@@ -1540,23 +1540,23 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>T-03B</t>
+          <t>T-06E</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>113.04</v>
+        <v>264.72</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>5041</v>
+        <v>6929</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>13024</v>
+        <v>14767</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>10827</v>
+        <v>11336</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>8850</v>
+        <v>6957</v>
       </c>
       <c r="G32" s="15">
         <f>D32/1000</f>
@@ -1575,23 +1575,23 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>T-03B</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>110.23</v>
+        <v>113.04</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>5065</v>
+        <v>5041</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>12784</v>
+        <v>14644</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10868</v>
+        <v>12365</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>9477</v>
+        <v>8850</v>
       </c>
       <c r="G33" s="8">
         <f>D33/1000</f>
@@ -1610,23 +1610,23 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>T-08A</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>14.18</v>
+        <v>110.23</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1756</v>
+        <v>5065</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>12754</v>
+        <v>14467</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>11882</v>
+        <v>12423</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>7912</v>
+        <v>9477</v>
       </c>
       <c r="G34" s="15">
         <f>D34/1000</f>
@@ -1645,23 +1645,23 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>T-06C</t>
+          <t>T-08A</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>31.74</v>
+        <v>14.18</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>2739</v>
+        <v>1756</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>12715</v>
+        <v>14333</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>11352</v>
+        <v>13414</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>7775</v>
+        <v>7912</v>
       </c>
       <c r="G35" s="8">
         <f>D35/1000</f>
@@ -1680,23 +1680,23 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>T-04A</t>
+          <t>T-04B</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>100.42</v>
+        <v>51.93</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>5093</v>
+        <v>3411</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>12054</v>
+        <v>13881</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>9975</v>
+        <v>12318</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>7977</v>
+        <v>7991</v>
       </c>
       <c r="G36" s="15">
         <f>D36/1000</f>
@@ -1715,23 +1715,23 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>T-04B</t>
+          <t>T-04A</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>51.93</v>
+        <v>100.42</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>3411</v>
+        <v>5093</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>12053</v>
+        <v>13864</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>10771</v>
+        <v>11513</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>7991</v>
+        <v>7977</v>
       </c>
       <c r="G37" s="8">
         <f>D37/1000</f>
@@ -1760,10 +1760,10 @@
         <v>9468</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>11735</v>
+        <v>13311</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>8876</v>
+        <v>10424</v>
       </c>
       <c r="F38" s="14" t="n">
         <v>7561</v>
@@ -1795,10 +1795,10 @@
         <v>5565</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>11069</v>
+        <v>12873</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>8542</v>
+        <v>10060</v>
       </c>
       <c r="F39" s="7" t="n">
         <v>7077</v>

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9F01D8-57A3-438C-9E39-648185A87408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BF8D80-A1F3-4582-927F-CF5D47F306D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34755" yWindow="2610" windowWidth="17625" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BF8D80-A1F3-4582-927F-CF5D47F306D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2675BE48-6499-43C4-8541-893665717D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2675BE48-6499-43C4-8541-893665717D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BBA2AD1-FAC8-43C4-849A-42B1D6480D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
   <si>
     <t>FAZENDA JAVA — distância dos talhões até a sede</t>
   </si>
@@ -72,109 +72,118 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-11B</t>
+  </si>
+  <si>
+    <t>T-11C</t>
+  </si>
+  <si>
     <t>T-11A</t>
   </si>
   <si>
+    <t>T-11D</t>
+  </si>
+  <si>
+    <t>T-13A</t>
+  </si>
+  <si>
+    <t>T-13B</t>
+  </si>
+  <si>
+    <t>T-13C</t>
+  </si>
+  <si>
     <t>T-13D</t>
   </si>
   <si>
-    <t>T-13C</t>
-  </si>
-  <si>
     <t>T-10A</t>
   </si>
   <si>
-    <t>T-11B</t>
-  </si>
-  <si>
-    <t>T-13B</t>
-  </si>
-  <si>
-    <t>T-11D</t>
-  </si>
-  <si>
     <t>T-12A</t>
   </si>
   <si>
-    <t>T-11C</t>
-  </si>
-  <si>
-    <t>T-13A</t>
+    <t>T-07A</t>
+  </si>
+  <si>
+    <t>T-09A</t>
+  </si>
+  <si>
+    <t>T-07B</t>
+  </si>
+  <si>
+    <t>T-14A</t>
+  </si>
+  <si>
+    <t>T-14D</t>
+  </si>
+  <si>
+    <t>T-15B</t>
+  </si>
+  <si>
+    <t>T-07D</t>
+  </si>
+  <si>
+    <t>T-07C</t>
+  </si>
+  <si>
+    <t>T-15C</t>
+  </si>
+  <si>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-01C</t>
+  </si>
+  <si>
+    <t>T-06B</t>
+  </si>
+  <si>
+    <t>T-06D</t>
+  </si>
+  <si>
+    <t>T-06E</t>
+  </si>
+  <si>
+    <t>T-06C</t>
+  </si>
+  <si>
+    <t>T-03B</t>
+  </si>
+  <si>
+    <t>T-03A</t>
+  </si>
+  <si>
+    <t>T-08A</t>
+  </si>
+  <si>
+    <t>T-01</t>
+  </si>
+  <si>
+    <t>T-04A</t>
+  </si>
+  <si>
+    <t>T-04B</t>
+  </si>
+  <si>
+    <t>T-01A</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-02</t>
   </si>
   <si>
     <t>T-09B</t>
   </si>
   <si>
-    <t>T-09A</t>
-  </si>
-  <si>
-    <t>T-15B</t>
-  </si>
-  <si>
-    <t>T-07B</t>
-  </si>
-  <si>
-    <t>T-08A</t>
-  </si>
-  <si>
-    <t>T-14A</t>
-  </si>
-  <si>
-    <t>T-14D</t>
-  </si>
-  <si>
-    <t>T-07A</t>
-  </si>
-  <si>
-    <t>T-07C</t>
-  </si>
-  <si>
-    <t>T-05</t>
-  </si>
-  <si>
-    <t>T-15C</t>
-  </si>
-  <si>
-    <t>T-07D</t>
-  </si>
-  <si>
-    <t>T-01C</t>
-  </si>
-  <si>
-    <t>T-03A</t>
-  </si>
-  <si>
-    <t>T-06C</t>
-  </si>
-  <si>
-    <t>T-06D</t>
-  </si>
-  <si>
-    <t>T-06B</t>
-  </si>
-  <si>
-    <t>T-06E</t>
-  </si>
-  <si>
-    <t>T-03B</t>
-  </si>
-  <si>
-    <t>T-04B</t>
-  </si>
-  <si>
-    <t>T-04A</t>
-  </si>
-  <si>
-    <t>T-01A</t>
-  </si>
-  <si>
-    <t>T-01</t>
-  </si>
-  <si>
-    <t>T-02</t>
-  </si>
-  <si>
-    <t>T-04</t>
+    <t>sem acesso</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>sem estrada até este talhão</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -253,7 +262,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,6 +308,17 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
@@ -310,7 +330,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,6 +345,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -349,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -370,13 +395,25 @@
     <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -745,31 +782,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>61.24</v>
+        <v>46.69</v>
       </c>
       <c r="C5" s="6">
-        <v>3271</v>
+        <v>3078</v>
       </c>
       <c r="D5" s="7">
-        <v>26692</v>
+        <v>23878</v>
       </c>
       <c r="E5" s="7">
-        <v>22261</v>
+        <v>23285</v>
       </c>
       <c r="F5" s="7">
-        <v>11475</v>
+        <v>11323</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:G39" si="0">D5/1000</f>
-        <v>26.692</v>
+        <f t="shared" ref="G5:G38" si="0">D5/1000</f>
+        <v>23.878</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" ref="H5:H39" si="1">E5/1000</f>
-        <v>22.260999999999999</v>
+        <f t="shared" ref="H5:H38" si="1">E5/1000</f>
+        <v>23.285</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I5:I39" si="2">IFERROR(D5/F5,"")</f>
-        <v>2.3261002178649237</v>
+        <f t="shared" ref="I5:I38" si="2">IFERROR(D5/F5,"")</f>
+        <v>2.1088050869910799</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -778,31 +815,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="12">
-        <v>61.56</v>
+        <v>52.01</v>
       </c>
       <c r="C6" s="13">
-        <v>3161</v>
+        <v>3100</v>
       </c>
       <c r="D6" s="14">
-        <v>26690</v>
+        <v>23878</v>
       </c>
       <c r="E6" s="14">
-        <v>22258</v>
+        <v>23285</v>
       </c>
       <c r="F6" s="14">
-        <v>11726</v>
+        <v>10871</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>26.69</v>
+        <v>23.878</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>22.257999999999999</v>
+        <v>23.285</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>2.2761384956506907</v>
+        <v>2.1964860638395733</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -811,31 +848,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>54.2</v>
+        <v>61.24</v>
       </c>
       <c r="C7" s="6">
-        <v>2992</v>
+        <v>3271</v>
       </c>
       <c r="D7" s="7">
-        <v>26326</v>
+        <v>23316</v>
       </c>
       <c r="E7" s="7">
-        <v>23076</v>
+        <v>22217</v>
       </c>
       <c r="F7" s="7">
-        <v>11982</v>
+        <v>11475</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>26.326000000000001</v>
+        <v>23.315999999999999</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>23.076000000000001</v>
+        <v>22.216999999999999</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>2.1971290268736436</v>
+        <v>2.0318954248366015</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -844,31 +881,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="12">
-        <v>67.819999999999993</v>
+        <v>70.47</v>
       </c>
       <c r="C8" s="13">
-        <v>4140</v>
+        <v>3481</v>
       </c>
       <c r="D8" s="14">
-        <v>25609</v>
+        <v>23316</v>
       </c>
       <c r="E8" s="14">
-        <v>20476</v>
+        <v>21484</v>
       </c>
       <c r="F8" s="14">
-        <v>10009</v>
+        <v>10886</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>25.609000000000002</v>
+        <v>23.315999999999999</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>20.475999999999999</v>
+        <v>21.484000000000002</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.5585972624637825</v>
+        <v>2.1418335476759141</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -877,31 +914,31 @@
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>46.69</v>
+        <v>53.65</v>
       </c>
       <c r="C9" s="6">
-        <v>3078</v>
+        <v>3197</v>
       </c>
       <c r="D9" s="7">
-        <v>25584</v>
+        <v>23063</v>
       </c>
       <c r="E9" s="7">
-        <v>23321</v>
+        <v>21642</v>
       </c>
       <c r="F9" s="7">
-        <v>11323</v>
+        <v>11107</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>25.584</v>
+        <v>23.062999999999999</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>23.321000000000002</v>
+        <v>21.641999999999999</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>2.25947187141217</v>
+        <v>2.0764382821644007</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -916,7 +953,7 @@
         <v>3110</v>
       </c>
       <c r="D10" s="14">
-        <v>24835</v>
+        <v>23063</v>
       </c>
       <c r="E10" s="14">
         <v>23063</v>
@@ -926,7 +963,7 @@
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>24.835000000000001</v>
+        <v>23.062999999999999</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
@@ -934,7 +971,7 @@
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>2.2255578456850973</v>
+        <v>2.066762254682319</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -943,31 +980,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>70.47</v>
+        <v>54.2</v>
       </c>
       <c r="C11" s="6">
-        <v>3481</v>
+        <v>2992</v>
       </c>
       <c r="D11" s="7">
-        <v>24724</v>
+        <v>23063</v>
       </c>
       <c r="E11" s="7">
-        <v>21521</v>
+        <v>23063</v>
       </c>
       <c r="F11" s="7">
-        <v>10886</v>
+        <v>11982</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>24.724</v>
+        <v>23.062999999999999</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>21.521000000000001</v>
+        <v>23.062999999999999</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>2.2711739849347787</v>
+        <v>1.9248038724753798</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -976,31 +1013,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>263.77999999999997</v>
+        <v>61.56</v>
       </c>
       <c r="C12" s="13">
-        <v>6934</v>
+        <v>3161</v>
       </c>
       <c r="D12" s="14">
-        <v>24642</v>
+        <v>23063</v>
       </c>
       <c r="E12" s="14">
-        <v>19867</v>
+        <v>22217</v>
       </c>
       <c r="F12" s="14">
-        <v>9384</v>
+        <v>11726</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>24.641999999999999</v>
+        <v>23.062999999999999</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>19.867000000000001</v>
+        <v>22.216999999999999</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>2.6259590792838874</v>
+        <v>1.9668258570697594</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1009,31 +1046,31 @@
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>52.01</v>
+        <v>67.819999999999993</v>
       </c>
       <c r="C13" s="6">
-        <v>3100</v>
+        <v>4140</v>
       </c>
       <c r="D13" s="7">
-        <v>24439</v>
+        <v>21541</v>
       </c>
       <c r="E13" s="7">
-        <v>23234</v>
+        <v>20437</v>
       </c>
       <c r="F13" s="7">
-        <v>10871</v>
+        <v>10009</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>24.439</v>
+        <v>21.541</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>23.234000000000002</v>
+        <v>20.437000000000001</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>2.248091251954742</v>
+        <v>2.1521630532520732</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1042,31 +1079,31 @@
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>53.65</v>
+        <v>263.77999999999997</v>
       </c>
       <c r="C14" s="13">
-        <v>3197</v>
+        <v>6934</v>
       </c>
       <c r="D14" s="14">
-        <v>24426</v>
+        <v>21515</v>
       </c>
       <c r="E14" s="14">
-        <v>21680</v>
+        <v>19824</v>
       </c>
       <c r="F14" s="14">
-        <v>11107</v>
+        <v>9384</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>24.425999999999998</v>
+        <v>21.515000000000001</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>21.68</v>
+        <v>19.824000000000002</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>2.1991536868641397</v>
+        <v>2.2927323103154307</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1075,31 +1112,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>51.45</v>
+        <v>50.64</v>
       </c>
       <c r="C15" s="6">
-        <v>3530</v>
+        <v>3002</v>
       </c>
       <c r="D15" s="7">
-        <v>21939</v>
+        <v>20762</v>
       </c>
       <c r="E15" s="7">
-        <v>20181</v>
+        <v>19097</v>
       </c>
       <c r="F15" s="7">
-        <v>9210</v>
+        <v>8442</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>21.939</v>
+        <v>20.762</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>20.181000000000001</v>
+        <v>19.097000000000001</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>2.3820846905537461</v>
+        <v>2.4593698175787728</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1114,25 +1151,25 @@
         <v>3147</v>
       </c>
       <c r="D16" s="14">
-        <v>21740</v>
+        <v>20360</v>
       </c>
       <c r="E16" s="14">
-        <v>20020</v>
+        <v>19963</v>
       </c>
       <c r="F16" s="14">
         <v>8842</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>21.74</v>
+        <v>20.36</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>20.02</v>
+        <v>19.963000000000001</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>2.4587197466636508</v>
+        <v>2.3026464600769057</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1141,31 +1178,31 @@
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>143</v>
+        <v>63.94</v>
       </c>
       <c r="C17" s="6">
-        <v>5499</v>
+        <v>3736</v>
       </c>
       <c r="D17" s="7">
-        <v>21533</v>
+        <v>20051</v>
       </c>
       <c r="E17" s="7">
-        <v>18280</v>
+        <v>19044</v>
       </c>
       <c r="F17" s="7">
-        <v>8307</v>
+        <v>9056</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>21.533000000000001</v>
+        <v>20.050999999999998</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>18.28</v>
+        <v>19.044</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>2.5921511977850007</v>
+        <v>2.2141121908127208</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1174,31 +1211,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>63.94</v>
+        <v>99.15</v>
       </c>
       <c r="C18" s="13">
-        <v>3736</v>
+        <v>4640</v>
       </c>
       <c r="D18" s="14">
-        <v>21375</v>
+        <v>19372</v>
       </c>
       <c r="E18" s="14">
-        <v>19092</v>
+        <v>18491</v>
       </c>
       <c r="F18" s="14">
-        <v>9056</v>
+        <v>8248</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>21.375</v>
+        <v>19.372</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>19.091999999999999</v>
+        <v>18.491</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>2.3603136042402828</v>
+        <v>2.3486905916585838</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1207,31 +1244,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>14.18</v>
+        <v>96.37</v>
       </c>
       <c r="C19" s="6">
-        <v>1756</v>
+        <v>4536</v>
       </c>
       <c r="D19" s="7">
-        <v>21275</v>
+        <v>19372</v>
       </c>
       <c r="E19" s="7">
-        <v>15931</v>
+        <v>18491</v>
       </c>
       <c r="F19" s="7">
-        <v>7912</v>
+        <v>8256</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>21.274999999999999</v>
+        <v>19.372</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>15.930999999999999</v>
+        <v>18.491</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>2.6889534883720931</v>
+        <v>2.3464147286821704</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1240,31 +1277,31 @@
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>99.15</v>
+        <v>143</v>
       </c>
       <c r="C20" s="13">
-        <v>4640</v>
+        <v>5499</v>
       </c>
       <c r="D20" s="14">
-        <v>21092</v>
+        <v>19372</v>
       </c>
       <c r="E20" s="14">
-        <v>18515</v>
+        <v>18466</v>
       </c>
       <c r="F20" s="14">
-        <v>8248</v>
+        <v>8307</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>21.091999999999999</v>
+        <v>19.372</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>18.515000000000001</v>
+        <v>18.466000000000001</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>2.5572259941804072</v>
+        <v>2.3320091489105574</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1273,31 +1310,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>96.37</v>
+        <v>43.25</v>
       </c>
       <c r="C21" s="6">
-        <v>4536</v>
+        <v>3108</v>
       </c>
       <c r="D21" s="7">
-        <v>21079</v>
+        <v>19127</v>
       </c>
       <c r="E21" s="7">
-        <v>18515</v>
+        <v>18329</v>
       </c>
       <c r="F21" s="7">
-        <v>8256</v>
+        <v>8461</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>21.079000000000001</v>
+        <v>19.126999999999999</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>18.515000000000001</v>
+        <v>18.329000000000001</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>2.553173449612403</v>
+        <v>2.2606074932041129</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1306,31 +1343,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>50.64</v>
+        <v>54.78</v>
       </c>
       <c r="C22" s="13">
-        <v>3002</v>
+        <v>3399</v>
       </c>
       <c r="D22" s="14">
-        <v>20999</v>
+        <v>19097</v>
       </c>
       <c r="E22" s="14">
-        <v>16635</v>
+        <v>18329</v>
       </c>
       <c r="F22" s="14">
-        <v>8442</v>
+        <v>9205</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>20.998999999999999</v>
+        <v>19.097000000000001</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>16.635000000000002</v>
+        <v>18.329000000000001</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>2.4874437337123902</v>
+        <v>2.0746333514394353</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1339,31 +1376,31 @@
         <v>30</v>
       </c>
       <c r="B23" s="5">
-        <v>54.78</v>
+        <v>95.86</v>
       </c>
       <c r="C23" s="6">
-        <v>3399</v>
+        <v>4455</v>
       </c>
       <c r="D23" s="7">
-        <v>20405</v>
+        <v>18515</v>
       </c>
       <c r="E23" s="7">
-        <v>18366</v>
+        <v>16914</v>
       </c>
       <c r="F23" s="7">
-        <v>9205</v>
+        <v>7221</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>20.405000000000001</v>
+        <v>18.515000000000001</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>18.366</v>
+        <v>16.914000000000001</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>2.2167300380228139</v>
+        <v>2.5640493006508795</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1378,25 +1415,25 @@
         <v>5071</v>
       </c>
       <c r="D24" s="14">
-        <v>20081</v>
+        <v>17362</v>
       </c>
       <c r="E24" s="14">
-        <v>16829</v>
+        <v>16756</v>
       </c>
       <c r="F24" s="14">
         <v>9352</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>20.081</v>
+        <v>17.361999999999998</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>16.829000000000001</v>
+        <v>16.756</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>2.1472412318220702</v>
+        <v>1.8565012831479897</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1405,31 +1442,31 @@
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>95.86</v>
+        <v>114.58</v>
       </c>
       <c r="C25" s="6">
-        <v>4455</v>
+        <v>5085</v>
       </c>
       <c r="D25" s="7">
-        <v>19928</v>
+        <v>17310</v>
       </c>
       <c r="E25" s="7">
-        <v>16953</v>
+        <v>15817</v>
       </c>
       <c r="F25" s="7">
-        <v>7221</v>
+        <v>8501</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>19.928000000000001</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>16.952999999999999</v>
+        <v>15.817</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>2.7597285694502145</v>
+        <v>2.0362310316433363</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1438,31 +1475,31 @@
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>43.25</v>
+        <v>73.88</v>
       </c>
       <c r="C26" s="13">
-        <v>3108</v>
+        <v>4134</v>
       </c>
       <c r="D26" s="14">
-        <v>19528</v>
+        <v>17310</v>
       </c>
       <c r="E26" s="14">
-        <v>16655</v>
+        <v>15702</v>
       </c>
       <c r="F26" s="14">
-        <v>8461</v>
+        <v>7712</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>19.527999999999999</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>16.655000000000001</v>
+        <v>15.702</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>2.3080014182720721</v>
+        <v>2.2445539419087135</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1471,31 +1508,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>114.58</v>
+        <v>148.91</v>
       </c>
       <c r="C27" s="6">
-        <v>5085</v>
+        <v>5858</v>
       </c>
       <c r="D27" s="7">
-        <v>19019</v>
+        <v>17310</v>
       </c>
       <c r="E27" s="7">
-        <v>15835</v>
+        <v>15702</v>
       </c>
       <c r="F27" s="7">
-        <v>8501</v>
+        <v>7712</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>19.018999999999998</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>15.835000000000001</v>
+        <v>15.702</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>2.2372662039760027</v>
+        <v>2.2445539419087135</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1504,31 +1541,31 @@
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>108.06</v>
+        <v>264.72000000000003</v>
       </c>
       <c r="C28" s="13">
-        <v>5283</v>
+        <v>6929</v>
       </c>
       <c r="D28" s="14">
-        <v>18650</v>
+        <v>17310</v>
       </c>
       <c r="E28" s="14">
-        <v>15201</v>
+        <v>13787</v>
       </c>
       <c r="F28" s="14">
-        <v>9732</v>
+        <v>6957</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>18.649999999999999</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>15.201000000000001</v>
+        <v>13.787000000000001</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.9163584052609945</v>
+        <v>2.4881414402759812</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1543,25 +1580,25 @@
         <v>2739</v>
       </c>
       <c r="D29" s="7">
-        <v>17942</v>
+        <v>16982</v>
       </c>
       <c r="E29" s="7">
-        <v>15441</v>
+        <v>16442</v>
       </c>
       <c r="F29" s="7">
         <v>7775</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>17.942</v>
+        <v>16.981999999999999</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>15.441000000000001</v>
+        <v>16.442</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>2.3076527331189709</v>
+        <v>2.1841800643086815</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1570,31 +1607,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>148.91</v>
+        <v>113.04</v>
       </c>
       <c r="C30" s="13">
-        <v>5858</v>
+        <v>5041</v>
       </c>
       <c r="D30" s="14">
-        <v>17938</v>
+        <v>16871</v>
       </c>
       <c r="E30" s="14">
-        <v>14870</v>
+        <v>14208</v>
       </c>
       <c r="F30" s="14">
-        <v>7712</v>
+        <v>8850</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>17.937999999999999</v>
+        <v>16.870999999999999</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>14.87</v>
+        <v>14.208</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>2.3259854771784232</v>
+        <v>1.9063276836158192</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1603,31 +1640,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>73.88</v>
+        <v>108.06</v>
       </c>
       <c r="C31" s="6">
-        <v>4134</v>
+        <v>5283</v>
       </c>
       <c r="D31" s="7">
-        <v>17911</v>
+        <v>16841</v>
       </c>
       <c r="E31" s="7">
-        <v>15728</v>
+        <v>15187</v>
       </c>
       <c r="F31" s="7">
-        <v>7712</v>
+        <v>9732</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>17.911000000000001</v>
+        <v>16.841000000000001</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>15.728</v>
+        <v>15.186999999999999</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>2.322484439834025</v>
+        <v>1.7304767776407728</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1636,31 +1673,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>264.72000000000003</v>
+        <v>14.18</v>
       </c>
       <c r="C32" s="13">
-        <v>6929</v>
+        <v>1756</v>
       </c>
       <c r="D32" s="14">
-        <v>17353</v>
+        <v>16629</v>
       </c>
       <c r="E32" s="14">
-        <v>13853</v>
+        <v>15894</v>
       </c>
       <c r="F32" s="14">
-        <v>6957</v>
+        <v>7912</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>17.353000000000002</v>
+        <v>16.629000000000001</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>13.853</v>
+        <v>15.894</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>2.4943222653442576</v>
+        <v>2.1017441860465116</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1669,31 +1706,31 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>113.04</v>
+        <v>110.23</v>
       </c>
       <c r="C33" s="6">
-        <v>5041</v>
+        <v>5065</v>
       </c>
       <c r="D33" s="7">
-        <v>17244</v>
+        <v>16426</v>
       </c>
       <c r="E33" s="7">
-        <v>14242</v>
+        <v>14267</v>
       </c>
       <c r="F33" s="7">
-        <v>8850</v>
+        <v>9477</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>17.244</v>
+        <v>16.425999999999998</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>14.242000000000001</v>
+        <v>14.266999999999999</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.9484745762711864</v>
+        <v>1.7332489184341036</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1702,31 +1739,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>51.93</v>
+        <v>100.42</v>
       </c>
       <c r="C34" s="13">
-        <v>3411</v>
+        <v>5093</v>
       </c>
       <c r="D34" s="14">
-        <v>17032</v>
+        <v>15892</v>
       </c>
       <c r="E34" s="14">
-        <v>14861</v>
+        <v>14294</v>
       </c>
       <c r="F34" s="14">
-        <v>7991</v>
+        <v>7977</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>17.032</v>
+        <v>15.891999999999999</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>14.861000000000001</v>
+        <v>14.294</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>2.1313978225503694</v>
+        <v>1.9922276545067068</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1735,31 +1772,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>100.42</v>
+        <v>51.93</v>
       </c>
       <c r="C35" s="6">
-        <v>5093</v>
+        <v>3411</v>
       </c>
       <c r="D35" s="7">
-        <v>16586</v>
+        <v>15849</v>
       </c>
       <c r="E35" s="7">
-        <v>13406</v>
+        <v>14818</v>
       </c>
       <c r="F35" s="7">
-        <v>7977</v>
+        <v>7991</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>16.585999999999999</v>
+        <v>15.849</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>13.406000000000001</v>
+        <v>14.818</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>2.0792277798671179</v>
+        <v>1.9833562758102865</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1774,25 +1811,25 @@
         <v>5134</v>
       </c>
       <c r="D36" s="14">
-        <v>16505</v>
+        <v>14757</v>
       </c>
       <c r="E36" s="14">
-        <v>13811</v>
+        <v>13779</v>
       </c>
       <c r="F36" s="14">
         <v>10367</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>16.504999999999999</v>
+        <v>14.757</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>13.811</v>
+        <v>13.779</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.5920709945017846</v>
+        <v>1.4234590527635766</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1801,31 +1838,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>110.23</v>
+        <v>107.45</v>
       </c>
       <c r="C37" s="6">
-        <v>5065</v>
+        <v>5565</v>
       </c>
       <c r="D37" s="7">
-        <v>16444</v>
+        <v>13280</v>
       </c>
       <c r="E37" s="7">
-        <v>12725</v>
+        <v>12164</v>
       </c>
       <c r="F37" s="7">
-        <v>9477</v>
+        <v>7077</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" si="0"/>
-        <v>16.443999999999999</v>
+        <v>13.28</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="1"/>
-        <v>12.725</v>
+        <v>12.164</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" si="2"/>
-        <v>1.7351482536667722</v>
+        <v>1.8765013423767134</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1840,85 +1877,84 @@
         <v>9468</v>
       </c>
       <c r="D38" s="14">
-        <v>15825</v>
+        <v>12672</v>
       </c>
       <c r="E38" s="14">
-        <v>10678</v>
+        <v>10636</v>
       </c>
       <c r="F38" s="14">
         <v>7561</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="0"/>
-        <v>15.824999999999999</v>
+        <v>12.672000000000001</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="1"/>
-        <v>10.678000000000001</v>
+        <v>10.635999999999999</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="2"/>
-        <v>2.0929771194286468</v>
+        <v>1.6759687871974607</v>
       </c>
       <c r="J38" s="17"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="5">
-        <v>107.45</v>
-      </c>
-      <c r="C39" s="6">
-        <v>5565</v>
-      </c>
-      <c r="D39" s="7">
-        <v>15610</v>
-      </c>
-      <c r="E39" s="7">
-        <v>12208</v>
-      </c>
-      <c r="F39" s="7">
-        <v>7077</v>
-      </c>
-      <c r="G39" s="8">
-        <f t="shared" si="0"/>
-        <v>15.61</v>
-      </c>
-      <c r="H39" s="8">
-        <f t="shared" si="1"/>
-        <v>12.208</v>
-      </c>
-      <c r="I39" s="9">
-        <f t="shared" si="2"/>
-        <v>2.2057368941641937</v>
-      </c>
-      <c r="J39" s="10"/>
+      <c r="B39" s="19">
+        <v>51.45</v>
+      </c>
+      <c r="C39" s="20">
+        <v>3530</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F39" s="22">
+        <v>9210</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="J39" s="25" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="19">
+      <c r="A41" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="27">
         <f>SUM(B5:B39)</f>
-        <v>3213.16</v>
-      </c>
-      <c r="D41" s="20">
+        <v>3213.1599999999989</v>
+      </c>
+      <c r="D41" s="28">
         <f>MAX(D5:D39)</f>
-        <v>26692</v>
-      </c>
-      <c r="G41" s="21">
+        <v>23878</v>
+      </c>
+      <c r="G41" s="29">
         <f>IFERROR(MAX(G5:G39),"")</f>
-        <v>26.692</v>
-      </c>
-      <c r="I41" s="22">
+        <v>23.878</v>
+      </c>
+      <c r="I41" s="30">
         <f>IFERROR(AVERAGE(I5:I39),"")</f>
-        <v>2.2882355100239358</v>
+        <v>2.0981985652324129</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="23" t="s">
-        <v>48</v>
+      <c r="A42" s="31" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1936,88 +1972,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>49</v>
+      <c r="A1" s="32" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>51</v>
+      <c r="A3" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>53</v>
+      <c r="A4" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>55</v>
+      <c r="A5" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>57</v>
+      <c r="A6" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>59</v>
+      <c r="A7" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>61</v>
+      <c r="A8" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>63</v>
+      <c r="A9" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>65</v>
+      <c r="A10" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>67</v>
+      <c r="A11" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>69</v>
+      <c r="A12" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BBA2AD1-FAC8-43C4-849A-42B1D6480D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BEC0FB-46A2-4187-A43F-BE65DFB6B447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,106 +72,106 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-11A</t>
+  </si>
+  <si>
+    <t>T-13C</t>
+  </si>
+  <si>
+    <t>T-13B</t>
+  </si>
+  <si>
     <t>T-11B</t>
   </si>
   <si>
+    <t>T-13D</t>
+  </si>
+  <si>
+    <t>T-11D</t>
+  </si>
+  <si>
+    <t>T-13A</t>
+  </si>
+  <si>
     <t>T-11C</t>
   </si>
   <si>
-    <t>T-11A</t>
-  </si>
-  <si>
-    <t>T-11D</t>
-  </si>
-  <si>
-    <t>T-13A</t>
-  </si>
-  <si>
-    <t>T-13B</t>
-  </si>
-  <si>
-    <t>T-13C</t>
-  </si>
-  <si>
-    <t>T-13D</t>
-  </si>
-  <si>
     <t>T-10A</t>
   </si>
   <si>
     <t>T-12A</t>
   </si>
   <si>
+    <t>T-14A</t>
+  </si>
+  <si>
+    <t>T-14D</t>
+  </si>
+  <si>
+    <t>T-07C</t>
+  </si>
+  <si>
+    <t>T-07D</t>
+  </si>
+  <si>
+    <t>T-15C</t>
+  </si>
+  <si>
+    <t>T-07B</t>
+  </si>
+  <si>
     <t>T-07A</t>
   </si>
   <si>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-01C</t>
+  </si>
+  <si>
+    <t>T-06B</t>
+  </si>
+  <si>
+    <t>T-06D</t>
+  </si>
+  <si>
+    <t>T-06E</t>
+  </si>
+  <si>
     <t>T-09A</t>
   </si>
   <si>
-    <t>T-07B</t>
-  </si>
-  <si>
-    <t>T-14A</t>
-  </si>
-  <si>
-    <t>T-14D</t>
+    <t>T-06C</t>
+  </si>
+  <si>
+    <t>T-03B</t>
+  </si>
+  <si>
+    <t>T-03A</t>
+  </si>
+  <si>
+    <t>T-08A</t>
+  </si>
+  <si>
+    <t>T-01</t>
+  </si>
+  <si>
+    <t>T-04A</t>
+  </si>
+  <si>
+    <t>T-04B</t>
+  </si>
+  <si>
+    <t>T-01A</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-02</t>
   </si>
   <si>
     <t>T-15B</t>
-  </si>
-  <si>
-    <t>T-07D</t>
-  </si>
-  <si>
-    <t>T-07C</t>
-  </si>
-  <si>
-    <t>T-15C</t>
-  </si>
-  <si>
-    <t>T-05</t>
-  </si>
-  <si>
-    <t>T-01C</t>
-  </si>
-  <si>
-    <t>T-06B</t>
-  </si>
-  <si>
-    <t>T-06D</t>
-  </si>
-  <si>
-    <t>T-06E</t>
-  </si>
-  <si>
-    <t>T-06C</t>
-  </si>
-  <si>
-    <t>T-03B</t>
-  </si>
-  <si>
-    <t>T-03A</t>
-  </si>
-  <si>
-    <t>T-08A</t>
-  </si>
-  <si>
-    <t>T-01</t>
-  </si>
-  <si>
-    <t>T-04A</t>
-  </si>
-  <si>
-    <t>T-04B</t>
-  </si>
-  <si>
-    <t>T-01A</t>
-  </si>
-  <si>
-    <t>T-04</t>
-  </si>
-  <si>
-    <t>T-02</t>
   </si>
   <si>
     <t>T-09B</t>
@@ -782,31 +782,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>46.69</v>
+        <v>61.24</v>
       </c>
       <c r="C5" s="6">
-        <v>3078</v>
+        <v>3271</v>
       </c>
       <c r="D5" s="7">
-        <v>23878</v>
+        <v>26425</v>
       </c>
       <c r="E5" s="7">
-        <v>23285</v>
+        <v>25324</v>
       </c>
       <c r="F5" s="7">
-        <v>11323</v>
+        <v>11475</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G38" si="0">D5/1000</f>
-        <v>23.878</v>
+        <v>26.425000000000001</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H38" si="1">E5/1000</f>
-        <v>23.285</v>
+        <v>25.324000000000002</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I38" si="2">IFERROR(D5/F5,"")</f>
-        <v>2.1088050869910799</v>
+        <v>2.3028322440087146</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -815,31 +815,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="12">
-        <v>52.01</v>
+        <v>54.2</v>
       </c>
       <c r="C6" s="13">
-        <v>3100</v>
+        <v>2992</v>
       </c>
       <c r="D6" s="14">
-        <v>23878</v>
+        <v>26143</v>
       </c>
       <c r="E6" s="14">
-        <v>23285</v>
+        <v>24523</v>
       </c>
       <c r="F6" s="14">
-        <v>10871</v>
+        <v>11982</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>23.878</v>
+        <v>26.143000000000001</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>23.285</v>
+        <v>24.523</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>2.1964860638395733</v>
+        <v>2.1818561175095978</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -848,31 +848,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>61.24</v>
+        <v>58.52</v>
       </c>
       <c r="C7" s="6">
-        <v>3271</v>
+        <v>3110</v>
       </c>
       <c r="D7" s="7">
-        <v>23316</v>
+        <v>24573</v>
       </c>
       <c r="E7" s="7">
-        <v>22217</v>
+        <v>23560</v>
       </c>
       <c r="F7" s="7">
-        <v>11475</v>
+        <v>11159</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>23.315999999999999</v>
+        <v>24.573</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>22.216999999999999</v>
+        <v>23.56</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>2.0318954248366015</v>
+        <v>2.2020790393404428</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -881,31 +881,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="12">
-        <v>70.47</v>
+        <v>46.69</v>
       </c>
       <c r="C8" s="13">
-        <v>3481</v>
+        <v>3078</v>
       </c>
       <c r="D8" s="14">
-        <v>23316</v>
+        <v>23903</v>
       </c>
       <c r="E8" s="14">
-        <v>21484</v>
+        <v>23311</v>
       </c>
       <c r="F8" s="14">
-        <v>10886</v>
+        <v>11323</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>23.315999999999999</v>
+        <v>23.902999999999999</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>21.484000000000002</v>
+        <v>23.311</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.1418335476759141</v>
+        <v>2.1110129824251525</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -914,31 +914,31 @@
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>53.65</v>
+        <v>61.56</v>
       </c>
       <c r="C9" s="6">
-        <v>3197</v>
+        <v>3161</v>
       </c>
       <c r="D9" s="7">
-        <v>23063</v>
+        <v>23559</v>
       </c>
       <c r="E9" s="7">
-        <v>21642</v>
+        <v>22243</v>
       </c>
       <c r="F9" s="7">
-        <v>11107</v>
+        <v>11726</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>23.062999999999999</v>
+        <v>23.559000000000001</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>21.641999999999999</v>
+        <v>22.242999999999999</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>2.0764382821644007</v>
+        <v>2.0091250213201435</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -947,31 +947,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="12">
-        <v>58.52</v>
+        <v>70.47</v>
       </c>
       <c r="C10" s="13">
-        <v>3110</v>
+        <v>3481</v>
       </c>
       <c r="D10" s="14">
-        <v>23063</v>
+        <v>23341</v>
       </c>
       <c r="E10" s="14">
-        <v>23063</v>
+        <v>21510</v>
       </c>
       <c r="F10" s="14">
-        <v>11159</v>
+        <v>10886</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>23.062999999999999</v>
+        <v>23.341000000000001</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>23.062999999999999</v>
+        <v>21.51</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>2.066762254682319</v>
+        <v>2.1441300753261068</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -980,31 +980,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>54.2</v>
+        <v>53.65</v>
       </c>
       <c r="C11" s="6">
-        <v>2992</v>
+        <v>3197</v>
       </c>
       <c r="D11" s="7">
-        <v>23063</v>
+        <v>23161</v>
       </c>
       <c r="E11" s="7">
-        <v>23063</v>
+        <v>21667</v>
       </c>
       <c r="F11" s="7">
-        <v>11982</v>
+        <v>11107</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>23.062999999999999</v>
+        <v>23.161000000000001</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>23.062999999999999</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>1.9248038724753798</v>
+        <v>2.0852615467723057</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1013,31 +1013,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>61.56</v>
+        <v>52.01</v>
       </c>
       <c r="C12" s="13">
-        <v>3161</v>
+        <v>3100</v>
       </c>
       <c r="D12" s="14">
-        <v>23063</v>
+        <v>23158</v>
       </c>
       <c r="E12" s="14">
-        <v>22217</v>
+        <v>22257</v>
       </c>
       <c r="F12" s="14">
-        <v>11726</v>
+        <v>10871</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>23.062999999999999</v>
+        <v>23.158000000000001</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>22.216999999999999</v>
+        <v>22.257000000000001</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>1.9668258570697594</v>
+        <v>2.1302548063655595</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1052,25 +1052,25 @@
         <v>4140</v>
       </c>
       <c r="D13" s="7">
-        <v>21541</v>
+        <v>22301</v>
       </c>
       <c r="E13" s="7">
-        <v>20437</v>
+        <v>20463</v>
       </c>
       <c r="F13" s="7">
         <v>10009</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>21.541</v>
+        <v>22.300999999999998</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>20.437000000000001</v>
+        <v>20.463000000000001</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>2.1521630532520732</v>
+        <v>2.2280947147567192</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1085,25 +1085,25 @@
         <v>6934</v>
       </c>
       <c r="D14" s="14">
-        <v>21515</v>
+        <v>21540</v>
       </c>
       <c r="E14" s="14">
-        <v>19824</v>
+        <v>19850</v>
       </c>
       <c r="F14" s="14">
         <v>9384</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>21.515000000000001</v>
+        <v>21.54</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>19.824000000000002</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>2.2927323103154307</v>
+        <v>2.2953964194373402</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1112,31 +1112,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>50.64</v>
+        <v>99.15</v>
       </c>
       <c r="C15" s="6">
-        <v>3002</v>
+        <v>4640</v>
       </c>
       <c r="D15" s="7">
-        <v>20762</v>
+        <v>19397</v>
       </c>
       <c r="E15" s="7">
-        <v>19097</v>
+        <v>18517</v>
       </c>
       <c r="F15" s="7">
-        <v>8442</v>
+        <v>8248</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>20.762</v>
+        <v>19.396999999999998</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>19.097000000000001</v>
+        <v>18.516999999999999</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>2.4593698175787728</v>
+        <v>2.3517216294859358</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1145,31 +1145,31 @@
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>51.15</v>
+        <v>96.37</v>
       </c>
       <c r="C16" s="13">
-        <v>3147</v>
+        <v>4536</v>
       </c>
       <c r="D16" s="14">
-        <v>20360</v>
+        <v>19397</v>
       </c>
       <c r="E16" s="14">
-        <v>19963</v>
+        <v>18517</v>
       </c>
       <c r="F16" s="14">
-        <v>8842</v>
+        <v>8256</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>20.36</v>
+        <v>19.396999999999998</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>19.963000000000001</v>
+        <v>18.516999999999999</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>2.3026464600769057</v>
+        <v>2.3494428294573644</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1178,31 +1178,31 @@
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>63.94</v>
+        <v>54.78</v>
       </c>
       <c r="C17" s="6">
-        <v>3736</v>
+        <v>3399</v>
       </c>
       <c r="D17" s="7">
-        <v>20051</v>
+        <v>18624</v>
       </c>
       <c r="E17" s="7">
-        <v>19044</v>
+        <v>18131</v>
       </c>
       <c r="F17" s="7">
-        <v>9056</v>
+        <v>9205</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>20.050999999999998</v>
+        <v>18.623999999999999</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>19.044</v>
+        <v>18.131</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>2.2141121908127208</v>
+        <v>2.0232482346550786</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1211,31 +1211,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>99.15</v>
+        <v>43.25</v>
       </c>
       <c r="C18" s="13">
-        <v>4640</v>
+        <v>3108</v>
       </c>
       <c r="D18" s="14">
-        <v>19372</v>
+        <v>18624</v>
       </c>
       <c r="E18" s="14">
-        <v>18491</v>
+        <v>18102</v>
       </c>
       <c r="F18" s="14">
-        <v>8248</v>
+        <v>8461</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>19.372</v>
+        <v>18.623999999999999</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>18.491</v>
+        <v>18.102</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>2.3486905916585838</v>
+        <v>2.2011582555253515</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1244,31 +1244,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>96.37</v>
+        <v>95.86</v>
       </c>
       <c r="C19" s="6">
-        <v>4536</v>
+        <v>4455</v>
       </c>
       <c r="D19" s="7">
-        <v>19372</v>
+        <v>18541</v>
       </c>
       <c r="E19" s="7">
-        <v>18491</v>
+        <v>16940</v>
       </c>
       <c r="F19" s="7">
-        <v>8256</v>
+        <v>7221</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>19.372</v>
+        <v>18.541</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>18.491</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>2.3464147286821704</v>
+        <v>2.5676499099847665</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1277,31 +1277,31 @@
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>143</v>
+        <v>63.94</v>
       </c>
       <c r="C20" s="13">
-        <v>5499</v>
+        <v>3736</v>
       </c>
       <c r="D20" s="14">
-        <v>19372</v>
+        <v>18184</v>
       </c>
       <c r="E20" s="14">
-        <v>18466</v>
+        <v>17178</v>
       </c>
       <c r="F20" s="14">
-        <v>8307</v>
+        <v>9056</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>19.372</v>
+        <v>18.184000000000001</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>18.466000000000001</v>
+        <v>17.178000000000001</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>2.3320091489105574</v>
+        <v>2.0079505300353357</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1310,31 +1310,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>43.25</v>
+        <v>50.64</v>
       </c>
       <c r="C21" s="6">
-        <v>3108</v>
+        <v>3002</v>
       </c>
       <c r="D21" s="7">
-        <v>19127</v>
+        <v>18131</v>
       </c>
       <c r="E21" s="7">
-        <v>18329</v>
+        <v>16467</v>
       </c>
       <c r="F21" s="7">
-        <v>8461</v>
+        <v>8442</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>19.126999999999999</v>
+        <v>18.131</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>18.329000000000001</v>
+        <v>16.466999999999999</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>2.2606074932041129</v>
+        <v>2.1477138118929164</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1343,31 +1343,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>54.78</v>
+        <v>114.01</v>
       </c>
       <c r="C22" s="13">
-        <v>3399</v>
+        <v>5071</v>
       </c>
       <c r="D22" s="14">
-        <v>19097</v>
+        <v>17388</v>
       </c>
       <c r="E22" s="14">
-        <v>18329</v>
+        <v>16782</v>
       </c>
       <c r="F22" s="14">
-        <v>9205</v>
+        <v>9352</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>19.097000000000001</v>
+        <v>17.388000000000002</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>18.329000000000001</v>
+        <v>16.782</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>2.0746333514394353</v>
+        <v>1.8592814371257484</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1376,31 +1376,31 @@
         <v>30</v>
       </c>
       <c r="B23" s="5">
-        <v>95.86</v>
+        <v>114.58</v>
       </c>
       <c r="C23" s="6">
-        <v>4455</v>
+        <v>5085</v>
       </c>
       <c r="D23" s="7">
-        <v>18515</v>
+        <v>17322</v>
       </c>
       <c r="E23" s="7">
-        <v>16914</v>
+        <v>15789</v>
       </c>
       <c r="F23" s="7">
-        <v>7221</v>
+        <v>8501</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>18.515000000000001</v>
+        <v>17.321999999999999</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>16.914000000000001</v>
+        <v>15.789</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>2.5640493006508795</v>
+        <v>2.0376426302787909</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1409,31 +1409,31 @@
         <v>31</v>
       </c>
       <c r="B24" s="12">
-        <v>114.01</v>
+        <v>73.88</v>
       </c>
       <c r="C24" s="13">
-        <v>5071</v>
+        <v>4134</v>
       </c>
       <c r="D24" s="14">
-        <v>17362</v>
+        <v>17322</v>
       </c>
       <c r="E24" s="14">
-        <v>16756</v>
+        <v>15727</v>
       </c>
       <c r="F24" s="14">
-        <v>9352</v>
+        <v>7712</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>17.361999999999998</v>
+        <v>17.321999999999999</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>16.756</v>
+        <v>15.727</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.8565012831479897</v>
+        <v>2.2461099585062239</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1442,31 +1442,31 @@
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>114.58</v>
+        <v>148.91</v>
       </c>
       <c r="C25" s="6">
-        <v>5085</v>
+        <v>5858</v>
       </c>
       <c r="D25" s="7">
-        <v>17310</v>
+        <v>17322</v>
       </c>
       <c r="E25" s="7">
-        <v>15817</v>
+        <v>15727</v>
       </c>
       <c r="F25" s="7">
-        <v>8501</v>
+        <v>7712</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>17.309999999999999</v>
+        <v>17.321999999999999</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>15.817</v>
+        <v>15.727</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>2.0362310316433363</v>
+        <v>2.2461099585062239</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1475,31 +1475,31 @@
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>73.88</v>
+        <v>264.72000000000003</v>
       </c>
       <c r="C26" s="13">
-        <v>4134</v>
+        <v>6929</v>
       </c>
       <c r="D26" s="14">
-        <v>17310</v>
+        <v>17322</v>
       </c>
       <c r="E26" s="14">
-        <v>15702</v>
+        <v>13813</v>
       </c>
       <c r="F26" s="14">
-        <v>7712</v>
+        <v>6957</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>17.309999999999999</v>
+        <v>17.321999999999999</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>15.702</v>
+        <v>13.813000000000001</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>2.2445539419087135</v>
+        <v>2.4898663216903838</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1508,31 +1508,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>148.91</v>
+        <v>51.15</v>
       </c>
       <c r="C27" s="6">
-        <v>5858</v>
+        <v>3147</v>
       </c>
       <c r="D27" s="7">
-        <v>17310</v>
+        <v>17266</v>
       </c>
       <c r="E27" s="7">
-        <v>15702</v>
+        <v>16869</v>
       </c>
       <c r="F27" s="7">
-        <v>7712</v>
+        <v>8842</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>17.309999999999999</v>
+        <v>17.265999999999998</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>15.702</v>
+        <v>16.869</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>2.2445539419087135</v>
+        <v>1.9527256276860439</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1541,31 +1541,31 @@
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>264.72000000000003</v>
+        <v>31.74</v>
       </c>
       <c r="C28" s="13">
-        <v>6929</v>
+        <v>2739</v>
       </c>
       <c r="D28" s="14">
-        <v>17310</v>
+        <v>16983</v>
       </c>
       <c r="E28" s="14">
-        <v>13787</v>
+        <v>16443</v>
       </c>
       <c r="F28" s="14">
-        <v>6957</v>
+        <v>7775</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>17.309999999999999</v>
+        <v>16.983000000000001</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>13.787000000000001</v>
+        <v>16.443000000000001</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>2.4881414402759812</v>
+        <v>2.1843086816720256</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1574,31 +1574,31 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>31.74</v>
+        <v>113.04</v>
       </c>
       <c r="C29" s="6">
-        <v>2739</v>
+        <v>5041</v>
       </c>
       <c r="D29" s="7">
-        <v>16982</v>
+        <v>16896</v>
       </c>
       <c r="E29" s="7">
-        <v>16442</v>
+        <v>14233</v>
       </c>
       <c r="F29" s="7">
-        <v>7775</v>
+        <v>8850</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>16.981999999999999</v>
+        <v>16.896000000000001</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>16.442</v>
+        <v>14.233000000000001</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>2.1841800643086815</v>
+        <v>1.9091525423728815</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1607,31 +1607,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>113.04</v>
+        <v>108.06</v>
       </c>
       <c r="C30" s="13">
-        <v>5041</v>
+        <v>5283</v>
       </c>
       <c r="D30" s="14">
-        <v>16871</v>
+        <v>16867</v>
       </c>
       <c r="E30" s="14">
-        <v>14208</v>
+        <v>15212</v>
       </c>
       <c r="F30" s="14">
-        <v>8850</v>
+        <v>9732</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>16.870999999999999</v>
+        <v>16.867000000000001</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>14.208</v>
+        <v>15.212</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.9063276836158192</v>
+        <v>1.73314837648993</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1640,31 +1640,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>108.06</v>
+        <v>14.18</v>
       </c>
       <c r="C31" s="6">
-        <v>5283</v>
+        <v>1756</v>
       </c>
       <c r="D31" s="7">
-        <v>16841</v>
+        <v>16654</v>
       </c>
       <c r="E31" s="7">
-        <v>15187</v>
+        <v>15919</v>
       </c>
       <c r="F31" s="7">
-        <v>9732</v>
+        <v>7912</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>16.841000000000001</v>
+        <v>16.654</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>15.186999999999999</v>
+        <v>15.919</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>1.7304767776407728</v>
+        <v>2.1049039433771486</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1673,31 +1673,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>14.18</v>
+        <v>110.23</v>
       </c>
       <c r="C32" s="13">
-        <v>1756</v>
+        <v>5065</v>
       </c>
       <c r="D32" s="14">
-        <v>16629</v>
+        <v>16452</v>
       </c>
       <c r="E32" s="14">
-        <v>15894</v>
+        <v>12673</v>
       </c>
       <c r="F32" s="14">
-        <v>7912</v>
+        <v>9477</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>16.629000000000001</v>
+        <v>16.452000000000002</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>15.894</v>
+        <v>12.673</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>2.1017441860465116</v>
+        <v>1.7359924026590694</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1706,31 +1706,31 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>110.23</v>
+        <v>100.42</v>
       </c>
       <c r="C33" s="6">
-        <v>5065</v>
+        <v>5093</v>
       </c>
       <c r="D33" s="7">
-        <v>16426</v>
+        <v>15893</v>
       </c>
       <c r="E33" s="7">
-        <v>14267</v>
+        <v>14319</v>
       </c>
       <c r="F33" s="7">
-        <v>9477</v>
+        <v>7977</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>16.425999999999998</v>
+        <v>15.893000000000001</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>14.266999999999999</v>
+        <v>14.319000000000001</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.7332489184341036</v>
+        <v>1.992353014917889</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1739,31 +1739,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>100.42</v>
+        <v>51.93</v>
       </c>
       <c r="C34" s="13">
-        <v>5093</v>
+        <v>3411</v>
       </c>
       <c r="D34" s="14">
-        <v>15892</v>
+        <v>15893</v>
       </c>
       <c r="E34" s="14">
-        <v>14294</v>
+        <v>14843</v>
       </c>
       <c r="F34" s="14">
-        <v>7977</v>
+        <v>7991</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>15.891999999999999</v>
+        <v>15.893000000000001</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>14.294</v>
+        <v>14.843</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.9922276545067068</v>
+        <v>1.988862470279064</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1772,31 +1772,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>51.93</v>
+        <v>109.74</v>
       </c>
       <c r="C35" s="6">
-        <v>3411</v>
+        <v>5134</v>
       </c>
       <c r="D35" s="7">
-        <v>15849</v>
+        <v>14709</v>
       </c>
       <c r="E35" s="7">
-        <v>14818</v>
+        <v>13784</v>
       </c>
       <c r="F35" s="7">
-        <v>7991</v>
+        <v>10367</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>15.849</v>
+        <v>14.709</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>14.818</v>
+        <v>13.784000000000001</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>1.9833562758102865</v>
+        <v>1.4188289765602393</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1805,31 +1805,31 @@
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>109.74</v>
+        <v>107.45</v>
       </c>
       <c r="C36" s="13">
-        <v>5134</v>
+        <v>5565</v>
       </c>
       <c r="D36" s="14">
-        <v>14757</v>
+        <v>13305</v>
       </c>
       <c r="E36" s="14">
-        <v>13779</v>
+        <v>12189</v>
       </c>
       <c r="F36" s="14">
-        <v>10367</v>
+        <v>7077</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>14.757</v>
+        <v>13.305</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>13.779</v>
+        <v>12.189</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.4234590527635766</v>
+        <v>1.8800339126748622</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1838,31 +1838,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>107.45</v>
+        <v>210.74</v>
       </c>
       <c r="C37" s="6">
-        <v>5565</v>
+        <v>9468</v>
       </c>
       <c r="D37" s="7">
-        <v>13280</v>
+        <v>12697</v>
       </c>
       <c r="E37" s="7">
-        <v>12164</v>
+        <v>10661</v>
       </c>
       <c r="F37" s="7">
-        <v>7077</v>
+        <v>7561</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" si="0"/>
-        <v>13.28</v>
+        <v>12.696999999999999</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="1"/>
-        <v>12.164</v>
+        <v>10.661</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" si="2"/>
-        <v>1.8765013423767134</v>
+        <v>1.6792752281444254</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1871,31 +1871,31 @@
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>210.74</v>
+        <v>143</v>
       </c>
       <c r="C38" s="13">
-        <v>9468</v>
+        <v>5499</v>
       </c>
       <c r="D38" s="14">
-        <v>12672</v>
+        <v>9711</v>
       </c>
       <c r="E38" s="14">
-        <v>10636</v>
+        <v>8841</v>
       </c>
       <c r="F38" s="14">
-        <v>7561</v>
+        <v>8307</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="0"/>
-        <v>12.672000000000001</v>
+        <v>9.7110000000000003</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="1"/>
-        <v>10.635999999999999</v>
+        <v>8.8409999999999993</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="2"/>
-        <v>1.6759687871974607</v>
+        <v>1.1690140845070423</v>
       </c>
       <c r="J38" s="17"/>
     </row>
@@ -1941,15 +1941,15 @@
       </c>
       <c r="D41" s="28">
         <f>MAX(D5:D39)</f>
-        <v>23878</v>
+        <v>26425</v>
       </c>
       <c r="G41" s="29">
         <f>IFERROR(MAX(G5:G39),"")</f>
-        <v>23.878</v>
+        <v>26.425000000000001</v>
       </c>
       <c r="I41" s="30">
         <f>IFERROR(AVERAGE(I5:I39),"")</f>
-        <v>2.0981985652324129</v>
+        <v>2.057839345169024</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BEC0FB-46A2-4187-A43F-BE65DFB6B447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE321A3-2676-4592-8198-3F82E6A1B007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,18 +90,24 @@
     <t>T-11D</t>
   </si>
   <si>
+    <t>T-11C</t>
+  </si>
+  <si>
     <t>T-13A</t>
   </si>
   <si>
-    <t>T-11C</t>
-  </si>
-  <si>
     <t>T-10A</t>
   </si>
   <si>
     <t>T-12A</t>
   </si>
   <si>
+    <t>T-15B</t>
+  </si>
+  <si>
+    <t>T-15C</t>
+  </si>
+  <si>
     <t>T-14A</t>
   </si>
   <si>
@@ -114,21 +120,18 @@
     <t>T-07D</t>
   </si>
   <si>
-    <t>T-15C</t>
-  </si>
-  <si>
     <t>T-07B</t>
   </si>
   <si>
     <t>T-07A</t>
   </si>
   <si>
+    <t>T-01C</t>
+  </si>
+  <si>
     <t>T-05</t>
   </si>
   <si>
-    <t>T-01C</t>
-  </si>
-  <si>
     <t>T-06B</t>
   </si>
   <si>
@@ -169,9 +172,6 @@
   </si>
   <si>
     <t>T-02</t>
-  </si>
-  <si>
-    <t>T-15B</t>
   </si>
   <si>
     <t>T-09B</t>
@@ -821,7 +821,7 @@
         <v>2992</v>
       </c>
       <c r="D6" s="14">
-        <v>26143</v>
+        <v>26144</v>
       </c>
       <c r="E6" s="14">
         <v>24523</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>26.143000000000001</v>
+        <v>26.143999999999998</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
@@ -839,7 +839,7 @@
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>2.1818561175095978</v>
+        <v>2.1819395760307128</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -857,7 +857,7 @@
         <v>24573</v>
       </c>
       <c r="E7" s="7">
-        <v>23560</v>
+        <v>23561</v>
       </c>
       <c r="F7" s="7">
         <v>11159</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>23.56</v>
+        <v>23.561</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
@@ -887,7 +887,7 @@
         <v>3078</v>
       </c>
       <c r="D8" s="14">
-        <v>23903</v>
+        <v>23904</v>
       </c>
       <c r="E8" s="14">
         <v>23311</v>
@@ -897,7 +897,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>23.902999999999999</v>
+        <v>23.904</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.1110129824251525</v>
+        <v>2.1111012982425152</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -920,7 +920,7 @@
         <v>3161</v>
       </c>
       <c r="D9" s="7">
-        <v>23559</v>
+        <v>23560</v>
       </c>
       <c r="E9" s="7">
         <v>22243</v>
@@ -930,7 +930,7 @@
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>23.559000000000001</v>
+        <v>23.56</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>2.0091250213201435</v>
+        <v>2.0092103018932286</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -953,25 +953,25 @@
         <v>3481</v>
       </c>
       <c r="D10" s="14">
-        <v>23341</v>
+        <v>23342</v>
       </c>
       <c r="E10" s="14">
-        <v>21510</v>
+        <v>21518</v>
       </c>
       <c r="F10" s="14">
         <v>10886</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>23.341000000000001</v>
+        <v>23.341999999999999</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>21.51</v>
+        <v>21.518000000000001</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>2.1441300753261068</v>
+        <v>2.1442219364321145</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -980,31 +980,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>53.65</v>
+        <v>52.01</v>
       </c>
       <c r="C11" s="6">
-        <v>3197</v>
+        <v>3100</v>
       </c>
       <c r="D11" s="7">
-        <v>23161</v>
+        <v>23158</v>
       </c>
       <c r="E11" s="7">
-        <v>21667</v>
+        <v>22257</v>
       </c>
       <c r="F11" s="7">
-        <v>11107</v>
+        <v>10871</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>23.161000000000001</v>
+        <v>23.158000000000001</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>21.667000000000002</v>
+        <v>22.257000000000001</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>2.0852615467723057</v>
+        <v>2.1302548063655595</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1013,31 +1013,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>52.01</v>
+        <v>53.65</v>
       </c>
       <c r="C12" s="13">
-        <v>3100</v>
+        <v>3197</v>
       </c>
       <c r="D12" s="14">
-        <v>23158</v>
+        <v>23119</v>
       </c>
       <c r="E12" s="14">
-        <v>22257</v>
+        <v>21668</v>
       </c>
       <c r="F12" s="14">
-        <v>10871</v>
+        <v>11107</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>23.158000000000001</v>
+        <v>23.119</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>22.257000000000001</v>
+        <v>21.667999999999999</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>2.1302548063655595</v>
+        <v>2.0814801476546321</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1052,7 +1052,7 @@
         <v>4140</v>
       </c>
       <c r="D13" s="7">
-        <v>22301</v>
+        <v>22302</v>
       </c>
       <c r="E13" s="7">
         <v>20463</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>22.300999999999998</v>
+        <v>22.302</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>2.2280947147567192</v>
+        <v>2.2281946248376463</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1085,7 +1085,7 @@
         <v>6934</v>
       </c>
       <c r="D14" s="14">
-        <v>21540</v>
+        <v>21751</v>
       </c>
       <c r="E14" s="14">
         <v>19850</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>21.54</v>
+        <v>21.751000000000001</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>2.2953964194373402</v>
+        <v>2.3178815004262576</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1112,31 +1112,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>99.15</v>
+        <v>143</v>
       </c>
       <c r="C15" s="6">
-        <v>4640</v>
+        <v>5499</v>
       </c>
       <c r="D15" s="7">
-        <v>19397</v>
+        <v>19403</v>
       </c>
       <c r="E15" s="7">
-        <v>18517</v>
+        <v>18480</v>
       </c>
       <c r="F15" s="7">
-        <v>8248</v>
+        <v>8307</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>19.396999999999998</v>
+        <v>19.402999999999999</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>18.516999999999999</v>
+        <v>18.48</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>2.3517216294859358</v>
+        <v>2.3357409413747443</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1145,31 +1145,31 @@
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>96.37</v>
+        <v>95.86</v>
       </c>
       <c r="C16" s="13">
-        <v>4536</v>
+        <v>4455</v>
       </c>
       <c r="D16" s="14">
-        <v>19397</v>
+        <v>19403</v>
       </c>
       <c r="E16" s="14">
-        <v>18517</v>
+        <v>16940</v>
       </c>
       <c r="F16" s="14">
-        <v>8256</v>
+        <v>7221</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>19.396999999999998</v>
+        <v>19.402999999999999</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>18.516999999999999</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>2.3494428294573644</v>
+        <v>2.6870239579005677</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1178,31 +1178,31 @@
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>54.78</v>
+        <v>99.15</v>
       </c>
       <c r="C17" s="6">
-        <v>3399</v>
+        <v>4640</v>
       </c>
       <c r="D17" s="7">
-        <v>18624</v>
+        <v>19398</v>
       </c>
       <c r="E17" s="7">
-        <v>18131</v>
+        <v>18506</v>
       </c>
       <c r="F17" s="7">
-        <v>9205</v>
+        <v>8248</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>18.623999999999999</v>
+        <v>19.398</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>18.131</v>
+        <v>18.506</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>2.0232482346550786</v>
+        <v>2.3518428709990302</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1211,31 +1211,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>43.25</v>
+        <v>96.37</v>
       </c>
       <c r="C18" s="13">
-        <v>3108</v>
+        <v>4536</v>
       </c>
       <c r="D18" s="14">
-        <v>18624</v>
+        <v>19398</v>
       </c>
       <c r="E18" s="14">
-        <v>18102</v>
+        <v>18506</v>
       </c>
       <c r="F18" s="14">
-        <v>8461</v>
+        <v>8256</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>18.623999999999999</v>
+        <v>19.398</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>18.102</v>
+        <v>18.506</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>2.2011582555253515</v>
+        <v>2.3495639534883721</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1244,31 +1244,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>95.86</v>
+        <v>54.78</v>
       </c>
       <c r="C19" s="6">
-        <v>4455</v>
+        <v>3399</v>
       </c>
       <c r="D19" s="7">
-        <v>18541</v>
+        <v>18604</v>
       </c>
       <c r="E19" s="7">
-        <v>16940</v>
+        <v>18132</v>
       </c>
       <c r="F19" s="7">
-        <v>7221</v>
+        <v>9205</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>18.541</v>
+        <v>18.603999999999999</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>16.940000000000001</v>
+        <v>18.132000000000001</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>2.5676499099847665</v>
+        <v>2.0210755024443237</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1277,31 +1277,31 @@
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>63.94</v>
+        <v>43.25</v>
       </c>
       <c r="C20" s="13">
-        <v>3736</v>
+        <v>3108</v>
       </c>
       <c r="D20" s="14">
-        <v>18184</v>
+        <v>18604</v>
       </c>
       <c r="E20" s="14">
-        <v>17178</v>
+        <v>18103</v>
       </c>
       <c r="F20" s="14">
-        <v>9056</v>
+        <v>8461</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>18.184000000000001</v>
+        <v>18.603999999999999</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>17.178000000000001</v>
+        <v>18.103000000000002</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>2.0079505300353357</v>
+        <v>2.1987944687389196</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1310,31 +1310,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>50.64</v>
+        <v>63.94</v>
       </c>
       <c r="C21" s="6">
-        <v>3002</v>
+        <v>3736</v>
       </c>
       <c r="D21" s="7">
-        <v>18131</v>
+        <v>18185</v>
       </c>
       <c r="E21" s="7">
-        <v>16467</v>
+        <v>17178</v>
       </c>
       <c r="F21" s="7">
-        <v>8442</v>
+        <v>9056</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>18.131</v>
+        <v>18.184999999999999</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>16.466999999999999</v>
+        <v>17.178000000000001</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>2.1477138118929164</v>
+        <v>2.0080609540636041</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1343,31 +1343,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>114.01</v>
+        <v>50.64</v>
       </c>
       <c r="C22" s="13">
-        <v>5071</v>
+        <v>3002</v>
       </c>
       <c r="D22" s="14">
-        <v>17388</v>
+        <v>18132</v>
       </c>
       <c r="E22" s="14">
-        <v>16782</v>
+        <v>16468</v>
       </c>
       <c r="F22" s="14">
-        <v>9352</v>
+        <v>8442</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>17.388000000000002</v>
+        <v>18.132000000000001</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>16.782</v>
+        <v>16.468</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>1.8592814371257484</v>
+        <v>2.1478322672352523</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1382,7 +1382,7 @@
         <v>5085</v>
       </c>
       <c r="D23" s="7">
-        <v>17322</v>
+        <v>17352</v>
       </c>
       <c r="E23" s="7">
         <v>15789</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>17.321999999999999</v>
+        <v>17.352</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>2.0376426302787909</v>
+        <v>2.0411716268674271</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1409,31 +1409,31 @@
         <v>31</v>
       </c>
       <c r="B24" s="12">
-        <v>73.88</v>
+        <v>114.01</v>
       </c>
       <c r="C24" s="13">
-        <v>4134</v>
+        <v>5071</v>
       </c>
       <c r="D24" s="14">
-        <v>17322</v>
+        <v>17352</v>
       </c>
       <c r="E24" s="14">
-        <v>15727</v>
+        <v>16762</v>
       </c>
       <c r="F24" s="14">
-        <v>7712</v>
+        <v>9352</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>17.321999999999999</v>
+        <v>17.352</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>15.727</v>
+        <v>16.762</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>2.2461099585062239</v>
+        <v>1.8554319931565439</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1442,16 +1442,16 @@
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>148.91</v>
+        <v>73.88</v>
       </c>
       <c r="C25" s="6">
-        <v>5858</v>
+        <v>4134</v>
       </c>
       <c r="D25" s="7">
         <v>17322</v>
       </c>
       <c r="E25" s="7">
-        <v>15727</v>
+        <v>15728</v>
       </c>
       <c r="F25" s="7">
         <v>7712</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>15.727</v>
+        <v>15.728</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
@@ -1475,19 +1475,19 @@
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>264.72000000000003</v>
+        <v>148.91</v>
       </c>
       <c r="C26" s="13">
-        <v>6929</v>
+        <v>5858</v>
       </c>
       <c r="D26" s="14">
         <v>17322</v>
       </c>
       <c r="E26" s="14">
-        <v>13813</v>
+        <v>15728</v>
       </c>
       <c r="F26" s="14">
-        <v>6957</v>
+        <v>7712</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
@@ -1495,11 +1495,11 @@
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>13.813000000000001</v>
+        <v>15.728</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>2.4898663216903838</v>
+        <v>2.2461099585062239</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1508,31 +1508,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>51.15</v>
+        <v>264.72000000000003</v>
       </c>
       <c r="C27" s="6">
-        <v>3147</v>
+        <v>6929</v>
       </c>
       <c r="D27" s="7">
-        <v>17266</v>
+        <v>17322</v>
       </c>
       <c r="E27" s="7">
-        <v>16869</v>
+        <v>13813</v>
       </c>
       <c r="F27" s="7">
-        <v>8842</v>
+        <v>6957</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>17.265999999999998</v>
+        <v>17.321999999999999</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>16.869</v>
+        <v>13.813000000000001</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>1.9527256276860439</v>
+        <v>2.4898663216903838</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1541,31 +1541,31 @@
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>31.74</v>
+        <v>51.15</v>
       </c>
       <c r="C28" s="13">
-        <v>2739</v>
+        <v>3147</v>
       </c>
       <c r="D28" s="14">
-        <v>16983</v>
+        <v>17267</v>
       </c>
       <c r="E28" s="14">
-        <v>16443</v>
+        <v>16869</v>
       </c>
       <c r="F28" s="14">
-        <v>7775</v>
+        <v>8842</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>16.983000000000001</v>
+        <v>17.266999999999999</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>16.443000000000001</v>
+        <v>16.869</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>2.1843086816720256</v>
+        <v>1.952838724270527</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1574,31 +1574,31 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>113.04</v>
+        <v>31.74</v>
       </c>
       <c r="C29" s="6">
-        <v>5041</v>
+        <v>2739</v>
       </c>
       <c r="D29" s="7">
-        <v>16896</v>
+        <v>16983</v>
       </c>
       <c r="E29" s="7">
-        <v>14233</v>
+        <v>16443</v>
       </c>
       <c r="F29" s="7">
-        <v>8850</v>
+        <v>7775</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>16.896000000000001</v>
+        <v>16.983000000000001</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>14.233000000000001</v>
+        <v>16.443000000000001</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.9091525423728815</v>
+        <v>2.1843086816720256</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1607,31 +1607,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>108.06</v>
+        <v>113.04</v>
       </c>
       <c r="C30" s="13">
-        <v>5283</v>
+        <v>5041</v>
       </c>
       <c r="D30" s="14">
-        <v>16867</v>
+        <v>16860</v>
       </c>
       <c r="E30" s="14">
-        <v>15212</v>
+        <v>14233</v>
       </c>
       <c r="F30" s="14">
-        <v>9732</v>
+        <v>8850</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>16.867000000000001</v>
+        <v>16.86</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>15.212</v>
+        <v>14.233000000000001</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.73314837648993</v>
+        <v>1.9050847457627118</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1640,31 +1640,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>14.18</v>
+        <v>108.06</v>
       </c>
       <c r="C31" s="6">
-        <v>1756</v>
+        <v>5283</v>
       </c>
       <c r="D31" s="7">
-        <v>16654</v>
+        <v>16822</v>
       </c>
       <c r="E31" s="7">
-        <v>15919</v>
+        <v>15212</v>
       </c>
       <c r="F31" s="7">
-        <v>7912</v>
+        <v>9732</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>16.654</v>
+        <v>16.821999999999999</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>15.919</v>
+        <v>15.212</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>2.1049039433771486</v>
+        <v>1.72852445540485</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1673,31 +1673,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>110.23</v>
+        <v>14.18</v>
       </c>
       <c r="C32" s="13">
-        <v>5065</v>
+        <v>1756</v>
       </c>
       <c r="D32" s="14">
-        <v>16452</v>
+        <v>16654</v>
       </c>
       <c r="E32" s="14">
-        <v>12673</v>
+        <v>15919</v>
       </c>
       <c r="F32" s="14">
-        <v>9477</v>
+        <v>7912</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>16.452000000000002</v>
+        <v>16.654</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>12.673</v>
+        <v>15.919</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>1.7359924026590694</v>
+        <v>2.1049039433771486</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1706,31 +1706,31 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>100.42</v>
+        <v>110.23</v>
       </c>
       <c r="C33" s="6">
-        <v>5093</v>
+        <v>5065</v>
       </c>
       <c r="D33" s="7">
-        <v>15893</v>
+        <v>16452</v>
       </c>
       <c r="E33" s="7">
-        <v>14319</v>
+        <v>12673</v>
       </c>
       <c r="F33" s="7">
-        <v>7977</v>
+        <v>9477</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>15.893000000000001</v>
+        <v>16.452000000000002</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>14.319000000000001</v>
+        <v>12.673</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.992353014917889</v>
+        <v>1.7359924026590694</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1739,19 +1739,19 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>51.93</v>
+        <v>100.42</v>
       </c>
       <c r="C34" s="13">
-        <v>3411</v>
+        <v>5093</v>
       </c>
       <c r="D34" s="14">
         <v>15893</v>
       </c>
       <c r="E34" s="14">
-        <v>14843</v>
+        <v>14319</v>
       </c>
       <c r="F34" s="14">
-        <v>7991</v>
+        <v>7977</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
@@ -1759,11 +1759,11 @@
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>14.843</v>
+        <v>14.319000000000001</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.988862470279064</v>
+        <v>1.992353014917889</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1772,31 +1772,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>109.74</v>
+        <v>51.93</v>
       </c>
       <c r="C35" s="6">
-        <v>5134</v>
+        <v>3411</v>
       </c>
       <c r="D35" s="7">
-        <v>14709</v>
+        <v>15893</v>
       </c>
       <c r="E35" s="7">
-        <v>13784</v>
+        <v>14843</v>
       </c>
       <c r="F35" s="7">
-        <v>10367</v>
+        <v>7991</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>14.709</v>
+        <v>15.893000000000001</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>13.784000000000001</v>
+        <v>14.843</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>1.4188289765602393</v>
+        <v>1.988862470279064</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1805,31 +1805,31 @@
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>107.45</v>
+        <v>109.74</v>
       </c>
       <c r="C36" s="13">
-        <v>5565</v>
+        <v>5134</v>
       </c>
       <c r="D36" s="14">
-        <v>13305</v>
+        <v>14709</v>
       </c>
       <c r="E36" s="14">
-        <v>12189</v>
+        <v>13784</v>
       </c>
       <c r="F36" s="14">
-        <v>7077</v>
+        <v>10367</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>13.305</v>
+        <v>14.709</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>12.189</v>
+        <v>13.784000000000001</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.8800339126748622</v>
+        <v>1.4188289765602393</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1838,31 +1838,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>210.74</v>
+        <v>107.45</v>
       </c>
       <c r="C37" s="6">
-        <v>9468</v>
+        <v>5565</v>
       </c>
       <c r="D37" s="7">
-        <v>12697</v>
+        <v>13305</v>
       </c>
       <c r="E37" s="7">
-        <v>10661</v>
+        <v>12189</v>
       </c>
       <c r="F37" s="7">
-        <v>7561</v>
+        <v>7077</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" si="0"/>
-        <v>12.696999999999999</v>
+        <v>13.305</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="1"/>
-        <v>10.661</v>
+        <v>12.189</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" si="2"/>
-        <v>1.6792752281444254</v>
+        <v>1.8800339126748622</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1871,31 +1871,31 @@
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>143</v>
+        <v>210.74</v>
       </c>
       <c r="C38" s="13">
-        <v>5499</v>
+        <v>9468</v>
       </c>
       <c r="D38" s="14">
-        <v>9711</v>
+        <v>12697</v>
       </c>
       <c r="E38" s="14">
-        <v>8841</v>
+        <v>10661</v>
       </c>
       <c r="F38" s="14">
-        <v>8307</v>
+        <v>7561</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="0"/>
-        <v>9.7110000000000003</v>
+        <v>12.696999999999999</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="1"/>
-        <v>8.8409999999999993</v>
+        <v>10.661</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="2"/>
-        <v>1.1690140845070423</v>
+        <v>1.6792752281444254</v>
       </c>
       <c r="J38" s="17"/>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I41" s="30">
         <f>IFERROR(AVERAGE(I5:I39),"")</f>
-        <v>2.057839345169024</v>
+        <v>2.0958478472331246</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE321A3-2676-4592-8198-3F82E6A1B007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3380EDA1-B342-44C5-8A03-764A2CFA1DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3380EDA1-B342-44C5-8A03-764A2CFA1DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54327963-2B85-454D-A107-A5F59A02DD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,15 +84,15 @@
     <t>T-11B</t>
   </si>
   <si>
+    <t>T-11C</t>
+  </si>
+  <si>
     <t>T-13D</t>
   </si>
   <si>
     <t>T-11D</t>
   </si>
   <si>
-    <t>T-11C</t>
-  </si>
-  <si>
     <t>T-13A</t>
   </si>
   <si>
@@ -144,34 +144,34 @@
     <t>T-09A</t>
   </si>
   <si>
+    <t>T-01A</t>
+  </si>
+  <si>
+    <t>T-03A</t>
+  </si>
+  <si>
+    <t>T-03B</t>
+  </si>
+  <si>
+    <t>T-01</t>
+  </si>
+  <si>
     <t>T-06C</t>
   </si>
   <si>
-    <t>T-03B</t>
-  </si>
-  <si>
-    <t>T-03A</t>
-  </si>
-  <si>
     <t>T-08A</t>
   </si>
   <si>
-    <t>T-01</t>
-  </si>
-  <si>
     <t>T-04A</t>
   </si>
   <si>
     <t>T-04B</t>
   </si>
   <si>
-    <t>T-01A</t>
+    <t>T-02</t>
   </si>
   <si>
     <t>T-04</t>
-  </si>
-  <si>
-    <t>T-02</t>
   </si>
   <si>
     <t>T-09B</t>
@@ -788,25 +788,25 @@
         <v>3271</v>
       </c>
       <c r="D5" s="7">
-        <v>26425</v>
+        <v>23839</v>
       </c>
       <c r="E5" s="7">
-        <v>25324</v>
+        <v>22737</v>
       </c>
       <c r="F5" s="7">
         <v>11475</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G38" si="0">D5/1000</f>
-        <v>26.425000000000001</v>
+        <v>23.838999999999999</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H38" si="1">E5/1000</f>
-        <v>25.324000000000002</v>
+        <v>22.736999999999998</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I38" si="2">IFERROR(D5/F5,"")</f>
-        <v>2.3028322440087146</v>
+        <v>2.0774727668845316</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -821,25 +821,25 @@
         <v>2992</v>
       </c>
       <c r="D6" s="14">
-        <v>26144</v>
+        <v>23624</v>
       </c>
       <c r="E6" s="14">
-        <v>24523</v>
+        <v>22003</v>
       </c>
       <c r="F6" s="14">
         <v>11982</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>26.143999999999998</v>
+        <v>23.623999999999999</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>24.523</v>
+        <v>22.003</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>2.1819395760307128</v>
+        <v>1.9716241028208981</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -854,25 +854,25 @@
         <v>3110</v>
       </c>
       <c r="D7" s="7">
-        <v>24573</v>
+        <v>22054</v>
       </c>
       <c r="E7" s="7">
-        <v>23561</v>
+        <v>21041</v>
       </c>
       <c r="F7" s="7">
         <v>11159</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>24.573</v>
+        <v>22.053999999999998</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>23.561</v>
+        <v>21.041</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>2.2020790393404428</v>
+        <v>1.9763419661259969</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -887,25 +887,25 @@
         <v>3078</v>
       </c>
       <c r="D8" s="14">
-        <v>23904</v>
+        <v>21384</v>
       </c>
       <c r="E8" s="14">
-        <v>23311</v>
+        <v>20791</v>
       </c>
       <c r="F8" s="14">
         <v>11323</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>23.904</v>
+        <v>21.384</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>23.311</v>
+        <v>20.791</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.1111012982425152</v>
+        <v>1.8885454384880331</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -914,31 +914,31 @@
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>61.56</v>
+        <v>52.01</v>
       </c>
       <c r="C9" s="6">
-        <v>3161</v>
+        <v>3100</v>
       </c>
       <c r="D9" s="7">
-        <v>23560</v>
+        <v>21081</v>
       </c>
       <c r="E9" s="7">
-        <v>22243</v>
+        <v>19730</v>
       </c>
       <c r="F9" s="7">
-        <v>11726</v>
+        <v>10871</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>23.56</v>
+        <v>21.081</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>22.242999999999999</v>
+        <v>19.73</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>2.0092103018932286</v>
+        <v>1.9391960261245516</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -947,31 +947,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="12">
-        <v>70.47</v>
+        <v>61.56</v>
       </c>
       <c r="C10" s="13">
-        <v>3481</v>
+        <v>3161</v>
       </c>
       <c r="D10" s="14">
-        <v>23342</v>
+        <v>21040</v>
       </c>
       <c r="E10" s="14">
-        <v>21518</v>
+        <v>19723</v>
       </c>
       <c r="F10" s="14">
-        <v>10886</v>
+        <v>11726</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>23.341999999999999</v>
+        <v>21.04</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>21.518000000000001</v>
+        <v>19.722999999999999</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>2.1442219364321145</v>
+        <v>1.7943032577178919</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -980,31 +980,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>52.01</v>
+        <v>70.47</v>
       </c>
       <c r="C11" s="6">
-        <v>3100</v>
+        <v>3481</v>
       </c>
       <c r="D11" s="7">
-        <v>23158</v>
+        <v>20822</v>
       </c>
       <c r="E11" s="7">
-        <v>22257</v>
+        <v>18999</v>
       </c>
       <c r="F11" s="7">
-        <v>10871</v>
+        <v>10886</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>23.158000000000001</v>
+        <v>20.821999999999999</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>22.257000000000001</v>
+        <v>18.998999999999999</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>2.1302548063655595</v>
+        <v>1.9127319492926695</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1019,25 +1019,25 @@
         <v>3197</v>
       </c>
       <c r="D12" s="14">
-        <v>23119</v>
+        <v>20599</v>
       </c>
       <c r="E12" s="14">
-        <v>21668</v>
+        <v>19148</v>
       </c>
       <c r="F12" s="14">
         <v>11107</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>23.119</v>
+        <v>20.599</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>21.667999999999999</v>
+        <v>19.148</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>2.0814801476546321</v>
+        <v>1.8545962005942198</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1052,25 +1052,25 @@
         <v>4140</v>
       </c>
       <c r="D13" s="7">
-        <v>22302</v>
+        <v>19774</v>
       </c>
       <c r="E13" s="7">
-        <v>20463</v>
+        <v>17939</v>
       </c>
       <c r="F13" s="7">
         <v>10009</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>22.302</v>
+        <v>19.774000000000001</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>20.463000000000001</v>
+        <v>17.939</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>2.2281946248376463</v>
+        <v>1.9756219402537716</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1085,25 +1085,25 @@
         <v>6934</v>
       </c>
       <c r="D14" s="14">
-        <v>21751</v>
+        <v>19231</v>
       </c>
       <c r="E14" s="14">
-        <v>19850</v>
+        <v>17330</v>
       </c>
       <c r="F14" s="14">
         <v>9384</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>21.751000000000001</v>
+        <v>19.231000000000002</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>19.850000000000001</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>2.3178815004262576</v>
+        <v>2.0493393009377665</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1118,25 +1118,25 @@
         <v>5499</v>
       </c>
       <c r="D15" s="7">
-        <v>19403</v>
+        <v>16883</v>
       </c>
       <c r="E15" s="7">
-        <v>18480</v>
+        <v>15960</v>
       </c>
       <c r="F15" s="7">
         <v>8307</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>19.402999999999999</v>
+        <v>16.882999999999999</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>18.48</v>
+        <v>15.96</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>2.3357409413747443</v>
+        <v>2.0323823281569759</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1151,25 +1151,25 @@
         <v>4455</v>
       </c>
       <c r="D16" s="14">
-        <v>19403</v>
+        <v>16883</v>
       </c>
       <c r="E16" s="14">
-        <v>16940</v>
+        <v>14420</v>
       </c>
       <c r="F16" s="14">
         <v>7221</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>19.402999999999999</v>
+        <v>16.882999999999999</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>16.940000000000001</v>
+        <v>14.42</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>2.6870239579005677</v>
+        <v>2.3380418224622628</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1184,25 +1184,25 @@
         <v>4640</v>
       </c>
       <c r="D17" s="7">
-        <v>19398</v>
+        <v>16878</v>
       </c>
       <c r="E17" s="7">
-        <v>18506</v>
+        <v>15986</v>
       </c>
       <c r="F17" s="7">
         <v>8248</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>19.398</v>
+        <v>16.878</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>18.506</v>
+        <v>15.986000000000001</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>2.3518428709990302</v>
+        <v>2.04631425800194</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1217,25 +1217,25 @@
         <v>4536</v>
       </c>
       <c r="D18" s="14">
-        <v>19398</v>
+        <v>16878</v>
       </c>
       <c r="E18" s="14">
-        <v>18506</v>
+        <v>15986</v>
       </c>
       <c r="F18" s="14">
         <v>8256</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>19.398</v>
+        <v>16.878</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>18.506</v>
+        <v>15.986000000000001</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>2.3495639534883721</v>
+        <v>2.0443313953488373</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1250,25 +1250,25 @@
         <v>3399</v>
       </c>
       <c r="D19" s="7">
-        <v>18604</v>
+        <v>16084</v>
       </c>
       <c r="E19" s="7">
-        <v>18132</v>
+        <v>15612</v>
       </c>
       <c r="F19" s="7">
         <v>9205</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>18.603999999999999</v>
+        <v>16.084</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>18.132000000000001</v>
+        <v>15.612</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>2.0210755024443237</v>
+        <v>1.7473112438891907</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1283,25 +1283,25 @@
         <v>3108</v>
       </c>
       <c r="D20" s="14">
-        <v>18604</v>
+        <v>16084</v>
       </c>
       <c r="E20" s="14">
-        <v>18103</v>
+        <v>15583</v>
       </c>
       <c r="F20" s="14">
         <v>8461</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>18.603999999999999</v>
+        <v>16.084</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>18.103000000000002</v>
+        <v>15.583</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>2.1987944687389196</v>
+        <v>1.9009573336485048</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1316,25 +1316,25 @@
         <v>3736</v>
       </c>
       <c r="D21" s="7">
-        <v>18185</v>
+        <v>15665</v>
       </c>
       <c r="E21" s="7">
-        <v>17178</v>
+        <v>14658</v>
       </c>
       <c r="F21" s="7">
         <v>9056</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>18.184999999999999</v>
+        <v>15.664999999999999</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>17.178000000000001</v>
+        <v>14.657999999999999</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>2.0080609540636041</v>
+        <v>1.7297924028268552</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1349,25 +1349,25 @@
         <v>3002</v>
       </c>
       <c r="D22" s="14">
-        <v>18132</v>
+        <v>15612</v>
       </c>
       <c r="E22" s="14">
-        <v>16468</v>
+        <v>13948</v>
       </c>
       <c r="F22" s="14">
         <v>8442</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>18.132000000000001</v>
+        <v>15.612</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>16.468</v>
+        <v>13.948</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>2.1478322672352523</v>
+        <v>1.8493248045486852</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1382,25 +1382,25 @@
         <v>5085</v>
       </c>
       <c r="D23" s="7">
-        <v>17352</v>
+        <v>14832</v>
       </c>
       <c r="E23" s="7">
-        <v>15789</v>
+        <v>13269</v>
       </c>
       <c r="F23" s="7">
         <v>8501</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>17.352</v>
+        <v>14.832000000000001</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>15.789</v>
+        <v>13.269</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>2.0411716268674271</v>
+        <v>1.7447359134219504</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1415,25 +1415,25 @@
         <v>5071</v>
       </c>
       <c r="D24" s="14">
-        <v>17352</v>
+        <v>14832</v>
       </c>
       <c r="E24" s="14">
-        <v>16762</v>
+        <v>14242</v>
       </c>
       <c r="F24" s="14">
         <v>9352</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>17.352</v>
+        <v>14.832000000000001</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>16.762</v>
+        <v>14.242000000000001</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.8554319931565439</v>
+        <v>1.5859709153122328</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1448,25 +1448,25 @@
         <v>4134</v>
       </c>
       <c r="D25" s="7">
-        <v>17322</v>
+        <v>14803</v>
       </c>
       <c r="E25" s="7">
-        <v>15728</v>
+        <v>13208</v>
       </c>
       <c r="F25" s="7">
         <v>7712</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>17.321999999999999</v>
+        <v>14.803000000000001</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>15.728</v>
+        <v>13.208</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>2.2461099585062239</v>
+        <v>1.9194761410788381</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1481,25 +1481,25 @@
         <v>5858</v>
       </c>
       <c r="D26" s="14">
-        <v>17322</v>
+        <v>14803</v>
       </c>
       <c r="E26" s="14">
-        <v>15728</v>
+        <v>13208</v>
       </c>
       <c r="F26" s="14">
         <v>7712</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>17.321999999999999</v>
+        <v>14.803000000000001</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>15.728</v>
+        <v>13.208</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>2.2461099585062239</v>
+        <v>1.9194761410788381</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1514,25 +1514,25 @@
         <v>6929</v>
       </c>
       <c r="D27" s="7">
-        <v>17322</v>
+        <v>14803</v>
       </c>
       <c r="E27" s="7">
-        <v>13813</v>
+        <v>11293</v>
       </c>
       <c r="F27" s="7">
         <v>6957</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>17.321999999999999</v>
+        <v>14.803000000000001</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>13.813000000000001</v>
+        <v>11.292999999999999</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>2.4898663216903838</v>
+        <v>2.1277849647836713</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1547,25 +1547,25 @@
         <v>3147</v>
       </c>
       <c r="D28" s="14">
-        <v>17267</v>
+        <v>14747</v>
       </c>
       <c r="E28" s="14">
-        <v>16869</v>
+        <v>14349</v>
       </c>
       <c r="F28" s="14">
         <v>8842</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>17.266999999999999</v>
+        <v>14.747</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>16.869</v>
+        <v>14.349</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.952838724270527</v>
+        <v>1.6678353313729926</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1574,31 +1574,31 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>31.74</v>
+        <v>109.74</v>
       </c>
       <c r="C29" s="6">
-        <v>2739</v>
+        <v>5134</v>
       </c>
       <c r="D29" s="7">
-        <v>16983</v>
+        <v>14708</v>
       </c>
       <c r="E29" s="7">
-        <v>16443</v>
+        <v>13783</v>
       </c>
       <c r="F29" s="7">
-        <v>7775</v>
+        <v>10367</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>16.983000000000001</v>
+        <v>14.708</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>16.443000000000001</v>
+        <v>13.782999999999999</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>2.1843086816720256</v>
+        <v>1.4187325166393363</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1607,31 +1607,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>113.04</v>
+        <v>108.06</v>
       </c>
       <c r="C30" s="13">
-        <v>5041</v>
+        <v>5283</v>
       </c>
       <c r="D30" s="14">
-        <v>16860</v>
+        <v>14602</v>
       </c>
       <c r="E30" s="14">
-        <v>14233</v>
+        <v>13332</v>
       </c>
       <c r="F30" s="14">
-        <v>8850</v>
+        <v>9732</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>16.86</v>
+        <v>14.602</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>14.233000000000001</v>
+        <v>13.332000000000001</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.9050847457627118</v>
+        <v>1.5004110152075627</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1640,31 +1640,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>108.06</v>
+        <v>113.04</v>
       </c>
       <c r="C31" s="6">
-        <v>5283</v>
+        <v>5041</v>
       </c>
       <c r="D31" s="7">
-        <v>16822</v>
+        <v>14602</v>
       </c>
       <c r="E31" s="7">
-        <v>15212</v>
+        <v>12353</v>
       </c>
       <c r="F31" s="7">
-        <v>9732</v>
+        <v>8850</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>16.821999999999999</v>
+        <v>14.602</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>15.212</v>
+        <v>12.353</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>1.72852445540485</v>
+        <v>1.6499435028248588</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1673,31 +1673,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>14.18</v>
+        <v>110.23</v>
       </c>
       <c r="C32" s="13">
-        <v>1756</v>
+        <v>5065</v>
       </c>
       <c r="D32" s="14">
-        <v>16654</v>
+        <v>14572</v>
       </c>
       <c r="E32" s="14">
-        <v>15919</v>
+        <v>12412</v>
       </c>
       <c r="F32" s="14">
-        <v>7912</v>
+        <v>9477</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>16.654</v>
+        <v>14.571999999999999</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>15.919</v>
+        <v>12.412000000000001</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>2.1049039433771486</v>
+        <v>1.5376173894692413</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1706,31 +1706,31 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>110.23</v>
+        <v>31.74</v>
       </c>
       <c r="C33" s="6">
-        <v>5065</v>
+        <v>2739</v>
       </c>
       <c r="D33" s="7">
-        <v>16452</v>
+        <v>14463</v>
       </c>
       <c r="E33" s="7">
-        <v>12673</v>
+        <v>13923</v>
       </c>
       <c r="F33" s="7">
-        <v>9477</v>
+        <v>7775</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>16.452000000000002</v>
+        <v>14.462999999999999</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>12.673</v>
+        <v>13.923</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.7359924026590694</v>
+        <v>1.8601929260450161</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1739,31 +1739,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>100.42</v>
+        <v>14.18</v>
       </c>
       <c r="C34" s="13">
-        <v>5093</v>
+        <v>1756</v>
       </c>
       <c r="D34" s="14">
-        <v>15893</v>
+        <v>14135</v>
       </c>
       <c r="E34" s="14">
-        <v>14319</v>
+        <v>13400</v>
       </c>
       <c r="F34" s="14">
-        <v>7977</v>
+        <v>7912</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>15.893000000000001</v>
+        <v>14.135</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>14.319000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.992353014917889</v>
+        <v>1.7865267947421637</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1772,31 +1772,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>51.93</v>
+        <v>100.42</v>
       </c>
       <c r="C35" s="6">
-        <v>3411</v>
+        <v>5093</v>
       </c>
       <c r="D35" s="7">
-        <v>15893</v>
+        <v>13645</v>
       </c>
       <c r="E35" s="7">
-        <v>14843</v>
+        <v>12352</v>
       </c>
       <c r="F35" s="7">
-        <v>7991</v>
+        <v>7977</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>15.893000000000001</v>
+        <v>13.645</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>14.843</v>
+        <v>12.352</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>1.988862470279064</v>
+        <v>1.7105428105804188</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1805,31 +1805,31 @@
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>109.74</v>
+        <v>51.93</v>
       </c>
       <c r="C36" s="13">
-        <v>5134</v>
+        <v>3411</v>
       </c>
       <c r="D36" s="14">
-        <v>14709</v>
+        <v>13645</v>
       </c>
       <c r="E36" s="14">
-        <v>13784</v>
+        <v>12323</v>
       </c>
       <c r="F36" s="14">
-        <v>10367</v>
+        <v>7991</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>14.709</v>
+        <v>13.645</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>13.784000000000001</v>
+        <v>12.323</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.4188289765602393</v>
+        <v>1.7075459892378926</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1838,31 +1838,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>107.45</v>
+        <v>210.74</v>
       </c>
       <c r="C37" s="6">
-        <v>5565</v>
+        <v>9468</v>
       </c>
       <c r="D37" s="7">
-        <v>13305</v>
+        <v>12697</v>
       </c>
       <c r="E37" s="7">
-        <v>12189</v>
+        <v>10412</v>
       </c>
       <c r="F37" s="7">
-        <v>7077</v>
+        <v>7561</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" si="0"/>
-        <v>13.305</v>
+        <v>12.696999999999999</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="1"/>
-        <v>12.189</v>
+        <v>10.412000000000001</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" si="2"/>
-        <v>1.8800339126748622</v>
+        <v>1.6792752281444254</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1871,31 +1871,31 @@
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>210.74</v>
+        <v>107.45</v>
       </c>
       <c r="C38" s="13">
-        <v>9468</v>
+        <v>5565</v>
       </c>
       <c r="D38" s="14">
-        <v>12697</v>
+        <v>11425</v>
       </c>
       <c r="E38" s="14">
-        <v>10661</v>
+        <v>10041</v>
       </c>
       <c r="F38" s="14">
-        <v>7561</v>
+        <v>7077</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="0"/>
-        <v>12.696999999999999</v>
+        <v>11.425000000000001</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="1"/>
-        <v>10.661</v>
+        <v>10.041</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="2"/>
-        <v>1.6792752281444254</v>
+        <v>1.6143846262540624</v>
       </c>
       <c r="J38" s="17"/>
     </row>
@@ -1941,15 +1941,15 @@
       </c>
       <c r="D41" s="28">
         <f>MAX(D5:D39)</f>
-        <v>26425</v>
+        <v>23839</v>
       </c>
       <c r="G41" s="29">
         <f>IFERROR(MAX(G5:G39),"")</f>
-        <v>26.425000000000001</v>
+        <v>23.838999999999999</v>
       </c>
       <c r="I41" s="30">
         <f>IFERROR(AVERAGE(I5:I39),"")</f>
-        <v>2.0958478472331246</v>
+        <v>1.8399611983622675</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54327963-2B85-454D-A107-A5F59A02DD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822337A6-3571-4972-ADAE-0EB8A85E8243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -788,7 +788,7 @@
         <v>3271</v>
       </c>
       <c r="D5" s="7">
-        <v>23839</v>
+        <v>23838</v>
       </c>
       <c r="E5" s="7">
         <v>22737</v>
@@ -798,7 +798,7 @@
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G38" si="0">D5/1000</f>
-        <v>23.838999999999999</v>
+        <v>23.838000000000001</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H38" si="1">E5/1000</f>
@@ -806,7 +806,7 @@
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I38" si="2">IFERROR(D5/F5,"")</f>
-        <v>2.0774727668845316</v>
+        <v>2.0773856209150328</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -854,7 +854,7 @@
         <v>3110</v>
       </c>
       <c r="D7" s="7">
-        <v>22054</v>
+        <v>22053</v>
       </c>
       <c r="E7" s="7">
         <v>21041</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>22.053999999999998</v>
+        <v>22.053000000000001</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>1.9763419661259969</v>
+        <v>1.9762523523613227</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -989,7 +989,7 @@
         <v>20822</v>
       </c>
       <c r="E11" s="7">
-        <v>18999</v>
+        <v>18998</v>
       </c>
       <c r="F11" s="7">
         <v>10886</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>18.998999999999999</v>
+        <v>18.998000000000001</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
@@ -1448,7 +1448,7 @@
         <v>4134</v>
       </c>
       <c r="D25" s="7">
-        <v>14803</v>
+        <v>14802</v>
       </c>
       <c r="E25" s="7">
         <v>13208</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>14.803000000000001</v>
+        <v>14.802</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>1.9194761410788381</v>
+        <v>1.9193464730290457</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1481,7 +1481,7 @@
         <v>5858</v>
       </c>
       <c r="D26" s="14">
-        <v>14803</v>
+        <v>14802</v>
       </c>
       <c r="E26" s="14">
         <v>13208</v>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>14.803000000000001</v>
+        <v>14.802</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>1.9194761410788381</v>
+        <v>1.9193464730290457</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1514,25 +1514,25 @@
         <v>6929</v>
       </c>
       <c r="D27" s="7">
-        <v>14803</v>
+        <v>14802</v>
       </c>
       <c r="E27" s="7">
-        <v>11293</v>
+        <v>11292</v>
       </c>
       <c r="F27" s="7">
         <v>6957</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>14.803000000000001</v>
+        <v>14.802</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>11.292999999999999</v>
+        <v>11.292</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>2.1277849647836713</v>
+        <v>2.1276412246658043</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1613,7 +1613,7 @@
         <v>5283</v>
       </c>
       <c r="D30" s="14">
-        <v>14602</v>
+        <v>14601</v>
       </c>
       <c r="E30" s="14">
         <v>13332</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>14.602</v>
+        <v>14.601000000000001</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.5004110152075627</v>
+        <v>1.500308261405672</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1646,7 +1646,7 @@
         <v>5041</v>
       </c>
       <c r="D31" s="7">
-        <v>14602</v>
+        <v>14601</v>
       </c>
       <c r="E31" s="7">
         <v>12353</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>14.602</v>
+        <v>14.601000000000001</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>1.6499435028248588</v>
+        <v>1.6498305084745764</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1745,25 +1745,25 @@
         <v>1756</v>
       </c>
       <c r="D34" s="14">
-        <v>14135</v>
+        <v>14134</v>
       </c>
       <c r="E34" s="14">
-        <v>13400</v>
+        <v>13399</v>
       </c>
       <c r="F34" s="14">
         <v>7912</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>14.135</v>
+        <v>14.134</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>13.4</v>
+        <v>13.398999999999999</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.7865267947421637</v>
+        <v>1.7864004044489383</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1844,7 +1844,7 @@
         <v>9468</v>
       </c>
       <c r="D37" s="7">
-        <v>12697</v>
+        <v>12696</v>
       </c>
       <c r="E37" s="7">
         <v>10412</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="G37" s="8">
         <f t="shared" si="0"/>
-        <v>12.696999999999999</v>
+        <v>12.696</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="1"/>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="I37" s="9">
         <f t="shared" si="2"/>
-        <v>1.6792752281444254</v>
+        <v>1.6791429705065468</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1880,7 +1880,7 @@
         <v>11425</v>
       </c>
       <c r="E38" s="14">
-        <v>10041</v>
+        <v>10040</v>
       </c>
       <c r="F38" s="14">
         <v>7077</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H38" s="15">
         <f t="shared" si="1"/>
-        <v>10.041</v>
+        <v>10.039999999999999</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="2"/>
@@ -1941,15 +1941,15 @@
       </c>
       <c r="D41" s="28">
         <f>MAX(D5:D39)</f>
-        <v>23839</v>
+        <v>23838</v>
       </c>
       <c r="G41" s="29">
         <f>IFERROR(MAX(G5:G39),"")</f>
-        <v>23.838999999999999</v>
+        <v>23.838000000000001</v>
       </c>
       <c r="I41" s="30">
         <f>IFERROR(AVERAGE(I5:I39),"")</f>
-        <v>1.8399611983622675</v>
+        <v>1.8399301915377113</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822337A6-3571-4972-ADAE-0EB8A85E8243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AF115C-0828-4C2A-A595-8DFDDB60E21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>FAZENDA JAVA — distância dos talhões até a sede</t>
   </si>
@@ -144,6 +144,9 @@
     <t>T-09A</t>
   </si>
   <si>
+    <t>T-09B</t>
+  </si>
+  <si>
     <t>T-01A</t>
   </si>
   <si>
@@ -172,18 +175,6 @@
   </si>
   <si>
     <t>T-04</t>
-  </si>
-  <si>
-    <t>T-09B</t>
-  </si>
-  <si>
-    <t>sem acesso</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>sem estrada até este talhão</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -262,7 +253,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -308,17 +299,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
@@ -330,7 +310,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -345,11 +325,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -374,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -395,25 +370,13 @@
     <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -797,15 +760,15 @@
         <v>11475</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:G38" si="0">D5/1000</f>
+        <f t="shared" ref="G5:G39" si="0">D5/1000</f>
         <v>23.838000000000001</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" ref="H5:H38" si="1">E5/1000</f>
+        <f t="shared" ref="H5:H39" si="1">E5/1000</f>
         <v>22.736999999999998</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I5:I38" si="2">IFERROR(D5/F5,"")</f>
+        <f t="shared" ref="I5:I39" si="2">IFERROR(D5/F5,"")</f>
         <v>2.0773856209150328</v>
       </c>
       <c r="J5" s="10"/>
@@ -1574,31 +1537,31 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>109.74</v>
+        <v>51.45</v>
       </c>
       <c r="C29" s="6">
-        <v>5134</v>
+        <v>3530</v>
       </c>
       <c r="D29" s="7">
-        <v>14708</v>
+        <v>14709</v>
       </c>
       <c r="E29" s="7">
-        <v>13783</v>
+        <v>14709</v>
       </c>
       <c r="F29" s="7">
-        <v>10367</v>
+        <v>9210</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>14.708</v>
+        <v>14.709</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>13.782999999999999</v>
+        <v>14.709</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.4187325166393363</v>
+        <v>1.5970684039087948</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1607,31 +1570,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>108.06</v>
+        <v>109.74</v>
       </c>
       <c r="C30" s="13">
-        <v>5283</v>
+        <v>5134</v>
       </c>
       <c r="D30" s="14">
-        <v>14601</v>
+        <v>14708</v>
       </c>
       <c r="E30" s="14">
-        <v>13332</v>
+        <v>13783</v>
       </c>
       <c r="F30" s="14">
-        <v>9732</v>
+        <v>10367</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>14.601000000000001</v>
+        <v>14.708</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>13.332000000000001</v>
+        <v>13.782999999999999</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.500308261405672</v>
+        <v>1.4187325166393363</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1640,19 +1603,19 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>113.04</v>
+        <v>108.06</v>
       </c>
       <c r="C31" s="6">
-        <v>5041</v>
+        <v>5283</v>
       </c>
       <c r="D31" s="7">
         <v>14601</v>
       </c>
       <c r="E31" s="7">
-        <v>12353</v>
+        <v>13332</v>
       </c>
       <c r="F31" s="7">
-        <v>8850</v>
+        <v>9732</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
@@ -1660,11 +1623,11 @@
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>12.353</v>
+        <v>13.332000000000001</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>1.6498305084745764</v>
+        <v>1.500308261405672</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1673,31 +1636,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>110.23</v>
+        <v>113.04</v>
       </c>
       <c r="C32" s="13">
-        <v>5065</v>
+        <v>5041</v>
       </c>
       <c r="D32" s="14">
-        <v>14572</v>
+        <v>14601</v>
       </c>
       <c r="E32" s="14">
-        <v>12412</v>
+        <v>12353</v>
       </c>
       <c r="F32" s="14">
-        <v>9477</v>
+        <v>8850</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>14.571999999999999</v>
+        <v>14.601000000000001</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>12.412000000000001</v>
+        <v>12.353</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>1.5376173894692413</v>
+        <v>1.6498305084745764</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1706,31 +1669,31 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>31.74</v>
+        <v>110.23</v>
       </c>
       <c r="C33" s="6">
-        <v>2739</v>
+        <v>5065</v>
       </c>
       <c r="D33" s="7">
-        <v>14463</v>
+        <v>14572</v>
       </c>
       <c r="E33" s="7">
-        <v>13923</v>
+        <v>12412</v>
       </c>
       <c r="F33" s="7">
-        <v>7775</v>
+        <v>9477</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>14.462999999999999</v>
+        <v>14.571999999999999</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>13.923</v>
+        <v>12.412000000000001</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.8601929260450161</v>
+        <v>1.5376173894692413</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1739,31 +1702,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>14.18</v>
+        <v>31.74</v>
       </c>
       <c r="C34" s="13">
-        <v>1756</v>
+        <v>2739</v>
       </c>
       <c r="D34" s="14">
-        <v>14134</v>
+        <v>14463</v>
       </c>
       <c r="E34" s="14">
-        <v>13399</v>
+        <v>13923</v>
       </c>
       <c r="F34" s="14">
-        <v>7912</v>
+        <v>7775</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>14.134</v>
+        <v>14.462999999999999</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>13.398999999999999</v>
+        <v>13.923</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.7864004044489383</v>
+        <v>1.8601929260450161</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1772,31 +1735,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>100.42</v>
+        <v>14.18</v>
       </c>
       <c r="C35" s="6">
-        <v>5093</v>
+        <v>1756</v>
       </c>
       <c r="D35" s="7">
-        <v>13645</v>
+        <v>14134</v>
       </c>
       <c r="E35" s="7">
-        <v>12352</v>
+        <v>13399</v>
       </c>
       <c r="F35" s="7">
-        <v>7977</v>
+        <v>7912</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>13.645</v>
+        <v>14.134</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>12.352</v>
+        <v>13.398999999999999</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>1.7105428105804188</v>
+        <v>1.7864004044489383</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1805,19 +1768,19 @@
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>51.93</v>
+        <v>100.42</v>
       </c>
       <c r="C36" s="13">
-        <v>3411</v>
+        <v>5093</v>
       </c>
       <c r="D36" s="14">
         <v>13645</v>
       </c>
       <c r="E36" s="14">
-        <v>12323</v>
+        <v>12352</v>
       </c>
       <c r="F36" s="14">
-        <v>7991</v>
+        <v>7977</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
@@ -1825,11 +1788,11 @@
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>12.323</v>
+        <v>12.352</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.7075459892378926</v>
+        <v>1.7105428105804188</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1838,31 +1801,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>210.74</v>
+        <v>51.93</v>
       </c>
       <c r="C37" s="6">
-        <v>9468</v>
+        <v>3411</v>
       </c>
       <c r="D37" s="7">
-        <v>12696</v>
+        <v>13645</v>
       </c>
       <c r="E37" s="7">
-        <v>10412</v>
+        <v>12323</v>
       </c>
       <c r="F37" s="7">
-        <v>7561</v>
+        <v>7991</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" si="0"/>
-        <v>12.696</v>
+        <v>13.645</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="1"/>
-        <v>10.412000000000001</v>
+        <v>12.323</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" si="2"/>
-        <v>1.6791429705065468</v>
+        <v>1.7075459892378926</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1871,90 +1834,91 @@
         <v>45</v>
       </c>
       <c r="B38" s="12">
+        <v>210.74</v>
+      </c>
+      <c r="C38" s="13">
+        <v>9468</v>
+      </c>
+      <c r="D38" s="14">
+        <v>12696</v>
+      </c>
+      <c r="E38" s="14">
+        <v>10412</v>
+      </c>
+      <c r="F38" s="14">
+        <v>7561</v>
+      </c>
+      <c r="G38" s="15">
+        <f t="shared" si="0"/>
+        <v>12.696</v>
+      </c>
+      <c r="H38" s="15">
+        <f t="shared" si="1"/>
+        <v>10.412000000000001</v>
+      </c>
+      <c r="I38" s="16">
+        <f t="shared" si="2"/>
+        <v>1.6791429705065468</v>
+      </c>
+      <c r="J38" s="17"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="5">
         <v>107.45</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C39" s="6">
         <v>5565</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D39" s="7">
         <v>11425</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E39" s="7">
         <v>10040</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F39" s="7">
         <v>7077</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G39" s="8">
         <f t="shared" si="0"/>
         <v>11.425000000000001</v>
       </c>
-      <c r="H38" s="15">
+      <c r="H39" s="8">
         <f t="shared" si="1"/>
         <v>10.039999999999999</v>
       </c>
-      <c r="I38" s="16">
+      <c r="I39" s="9">
         <f t="shared" si="2"/>
         <v>1.6143846262540624</v>
       </c>
-      <c r="J38" s="17"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="19">
-        <v>51.45</v>
-      </c>
-      <c r="C39" s="20">
-        <v>3530</v>
-      </c>
-      <c r="D39" s="21" t="s">
+      <c r="J39" s="10"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E39" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F39" s="22">
-        <v>9210</v>
-      </c>
-      <c r="G39" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="H39" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="I39" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="J39" s="25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B41" s="27">
+      <c r="B41" s="19">
         <f>SUM(B5:B39)</f>
         <v>3213.1599999999989</v>
       </c>
-      <c r="D41" s="28">
+      <c r="D41" s="20">
         <f>MAX(D5:D39)</f>
         <v>23838</v>
       </c>
-      <c r="G41" s="29">
+      <c r="G41" s="21">
         <f>IFERROR(MAX(G5:G39),"")</f>
         <v>23.838000000000001</v>
       </c>
-      <c r="I41" s="30">
+      <c r="I41" s="22">
         <f>IFERROR(AVERAGE(I5:I39),"")</f>
-        <v>1.8399301915377113</v>
+        <v>1.8329912833197421</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="31" t="s">
-        <v>51</v>
+      <c r="A42" s="23" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1972,88 +1936,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="B4" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="34" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+      <c r="B5" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="34" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
+      <c r="B6" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="34" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
+      <c r="B7" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="34" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
+      <c r="B8" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="34" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="25" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="33" t="s">
+      <c r="B9" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="34" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="25" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
+      <c r="B10" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="34" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="25" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
+      <c r="B11" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="34" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="33" t="s">
+      <c r="B12" s="26" t="s">
         <v>69</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AF115C-0828-4C2A-A595-8DFDDB60E21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4789037E-37D8-4A98-A0D6-05F04E6E22B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4789037E-37D8-4A98-A0D6-05F04E6E22B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15603A78-ABD1-40D6-A3E4-305E01B81803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15603A78-ABD1-40D6-A3E4-305E01B81803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B953B4B-D05D-4746-84C3-BDCAF00A3FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -265,49 +265,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B953B4B-D05D-4746-84C3-BDCAF00A3FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CD597F-945E-47A1-ABB6-C5B0CC9024A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -144,10 +144,10 @@
     <t>T-09A</t>
   </si>
   <si>
+    <t>T-01A</t>
+  </si>
+  <si>
     <t>T-09B</t>
-  </si>
-  <si>
-    <t>T-01A</t>
   </si>
   <si>
     <t>T-03A</t>
@@ -265,58 +265,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -793,7 +784,7 @@
         <v>2992</v>
       </c>
       <c r="D6" s="14">
-        <v>23624</v>
+        <v>23623</v>
       </c>
       <c r="E6" s="14">
         <v>22003</v>
@@ -803,7 +794,7 @@
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>23.623999999999999</v>
+        <v>23.623000000000001</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
@@ -811,7 +802,7 @@
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>1.9716241028208981</v>
+        <v>1.9715406442997829</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -829,7 +820,7 @@
         <v>22053</v>
       </c>
       <c r="E7" s="7">
-        <v>21041</v>
+        <v>21040</v>
       </c>
       <c r="F7" s="7">
         <v>11159</v>
@@ -840,7 +831,7 @@
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>21.041</v>
+        <v>21.04</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
@@ -859,7 +850,7 @@
         <v>3078</v>
       </c>
       <c r="D8" s="14">
-        <v>21384</v>
+        <v>21383</v>
       </c>
       <c r="E8" s="14">
         <v>20791</v>
@@ -869,7 +860,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>21.384</v>
+        <v>21.382999999999999</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
@@ -877,7 +868,7 @@
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>1.8885454384880331</v>
+        <v>1.8884571226706703</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -892,25 +883,25 @@
         <v>3100</v>
       </c>
       <c r="D9" s="7">
-        <v>21081</v>
+        <v>21080</v>
       </c>
       <c r="E9" s="7">
-        <v>19730</v>
+        <v>19729</v>
       </c>
       <c r="F9" s="7">
         <v>10871</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>21.081</v>
+        <v>21.08</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>19.73</v>
+        <v>19.728999999999999</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>1.9391960261245516</v>
+        <v>1.9391040382669487</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -925,7 +916,7 @@
         <v>3161</v>
       </c>
       <c r="D10" s="14">
-        <v>21040</v>
+        <v>21039</v>
       </c>
       <c r="E10" s="14">
         <v>19723</v>
@@ -935,7 +926,7 @@
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>21.04</v>
+        <v>21.039000000000001</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
@@ -943,7 +934,7 @@
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>1.7943032577178919</v>
+        <v>1.7942179771448064</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -958,7 +949,7 @@
         <v>3481</v>
       </c>
       <c r="D11" s="7">
-        <v>20822</v>
+        <v>20821</v>
       </c>
       <c r="E11" s="7">
         <v>18998</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>20.821999999999999</v>
+        <v>20.821000000000002</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
@@ -976,7 +967,7 @@
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>1.9127319492926695</v>
+        <v>1.9126400881866619</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -994,7 +985,7 @@
         <v>20599</v>
       </c>
       <c r="E12" s="14">
-        <v>19148</v>
+        <v>19147</v>
       </c>
       <c r="F12" s="14">
         <v>11107</v>
@@ -1005,7 +996,7 @@
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>19.148</v>
+        <v>19.146999999999998</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
@@ -1024,7 +1015,7 @@
         <v>4140</v>
       </c>
       <c r="D13" s="7">
-        <v>19774</v>
+        <v>19773</v>
       </c>
       <c r="E13" s="7">
         <v>17939</v>
@@ -1034,7 +1025,7 @@
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>19.774000000000001</v>
+        <v>19.773</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
@@ -1042,7 +1033,7 @@
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>1.9756219402537716</v>
+        <v>1.9755220301728444</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1057,7 +1048,7 @@
         <v>6934</v>
       </c>
       <c r="D14" s="14">
-        <v>19231</v>
+        <v>19230</v>
       </c>
       <c r="E14" s="14">
         <v>17330</v>
@@ -1067,7 +1058,7 @@
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>19.231000000000002</v>
+        <v>19.23</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
@@ -1075,7 +1066,7 @@
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>2.0493393009377665</v>
+        <v>2.0492327365728902</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1090,7 +1081,7 @@
         <v>5499</v>
       </c>
       <c r="D15" s="7">
-        <v>16883</v>
+        <v>16882</v>
       </c>
       <c r="E15" s="7">
         <v>15960</v>
@@ -1100,7 +1091,7 @@
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>16.882999999999999</v>
+        <v>16.882000000000001</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
@@ -1108,7 +1099,7 @@
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>2.0323823281569759</v>
+        <v>2.0322619477549053</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1123,7 +1114,7 @@
         <v>4455</v>
       </c>
       <c r="D16" s="14">
-        <v>16883</v>
+        <v>16882</v>
       </c>
       <c r="E16" s="14">
         <v>14420</v>
@@ -1133,7 +1124,7 @@
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>16.882999999999999</v>
+        <v>16.882000000000001</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
@@ -1141,7 +1132,7 @@
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>2.3380418224622628</v>
+        <v>2.3379033374878824</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1156,25 +1147,25 @@
         <v>4640</v>
       </c>
       <c r="D17" s="7">
-        <v>16878</v>
+        <v>16877</v>
       </c>
       <c r="E17" s="7">
-        <v>15986</v>
+        <v>15985</v>
       </c>
       <c r="F17" s="7">
         <v>8248</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>16.878</v>
+        <v>16.876999999999999</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>15.986000000000001</v>
+        <v>15.984999999999999</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>2.04631425800194</v>
+        <v>2.046193016488846</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1189,25 +1180,25 @@
         <v>4536</v>
       </c>
       <c r="D18" s="14">
-        <v>16878</v>
+        <v>16877</v>
       </c>
       <c r="E18" s="14">
-        <v>15986</v>
+        <v>15985</v>
       </c>
       <c r="F18" s="14">
         <v>8256</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>16.878</v>
+        <v>16.876999999999999</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>15.986000000000001</v>
+        <v>15.984999999999999</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>2.0443313953488373</v>
+        <v>2.0442102713178296</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1222,25 +1213,25 @@
         <v>3399</v>
       </c>
       <c r="D19" s="7">
-        <v>16084</v>
+        <v>16083</v>
       </c>
       <c r="E19" s="7">
-        <v>15612</v>
+        <v>15611</v>
       </c>
       <c r="F19" s="7">
         <v>9205</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>16.084</v>
+        <v>16.082999999999998</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>15.612</v>
+        <v>15.611000000000001</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>1.7473112438891907</v>
+        <v>1.7472026072786528</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1255,25 +1246,25 @@
         <v>3108</v>
       </c>
       <c r="D20" s="14">
-        <v>16084</v>
+        <v>16083</v>
       </c>
       <c r="E20" s="14">
-        <v>15583</v>
+        <v>15582</v>
       </c>
       <c r="F20" s="14">
         <v>8461</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>16.084</v>
+        <v>16.082999999999998</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>15.583</v>
+        <v>15.582000000000001</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>1.9009573336485048</v>
+        <v>1.9008391443091832</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1288,7 +1279,7 @@
         <v>3736</v>
       </c>
       <c r="D21" s="7">
-        <v>15665</v>
+        <v>15664</v>
       </c>
       <c r="E21" s="7">
         <v>14658</v>
@@ -1298,7 +1289,7 @@
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>15.664999999999999</v>
+        <v>15.664</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
@@ -1306,7 +1297,7 @@
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>1.7297924028268552</v>
+        <v>1.7296819787985867</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1321,25 +1312,25 @@
         <v>3002</v>
       </c>
       <c r="D22" s="14">
-        <v>15612</v>
+        <v>15611</v>
       </c>
       <c r="E22" s="14">
-        <v>13948</v>
+        <v>13947</v>
       </c>
       <c r="F22" s="14">
         <v>8442</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>15.612</v>
+        <v>15.611000000000001</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>13.948</v>
+        <v>13.946999999999999</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>1.8493248045486852</v>
+        <v>1.8492063492063493</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1354,25 +1345,25 @@
         <v>5085</v>
       </c>
       <c r="D23" s="7">
-        <v>14832</v>
+        <v>14842</v>
       </c>
       <c r="E23" s="7">
-        <v>13269</v>
+        <v>13279</v>
       </c>
       <c r="F23" s="7">
         <v>8501</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>14.832000000000001</v>
+        <v>14.842000000000001</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>13.269</v>
+        <v>13.279</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>1.7447359134219504</v>
+        <v>1.7459122456181626</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1387,25 +1378,25 @@
         <v>5071</v>
       </c>
       <c r="D24" s="14">
-        <v>14832</v>
+        <v>14842</v>
       </c>
       <c r="E24" s="14">
-        <v>14242</v>
+        <v>14252</v>
       </c>
       <c r="F24" s="14">
         <v>9352</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>14.832000000000001</v>
+        <v>14.842000000000001</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>14.242000000000001</v>
+        <v>14.252000000000001</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.5859709153122328</v>
+        <v>1.5870402053036783</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1423,7 +1414,7 @@
         <v>14802</v>
       </c>
       <c r="E25" s="7">
-        <v>13208</v>
+        <v>13207</v>
       </c>
       <c r="F25" s="7">
         <v>7712</v>
@@ -1434,7 +1425,7 @@
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>13.208</v>
+        <v>13.207000000000001</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
@@ -1456,7 +1447,7 @@
         <v>14802</v>
       </c>
       <c r="E26" s="14">
-        <v>13208</v>
+        <v>13207</v>
       </c>
       <c r="F26" s="14">
         <v>7712</v>
@@ -1467,7 +1458,7 @@
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>13.208</v>
+        <v>13.207000000000001</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
@@ -1489,7 +1480,7 @@
         <v>14802</v>
       </c>
       <c r="E27" s="7">
-        <v>11292</v>
+        <v>11307</v>
       </c>
       <c r="F27" s="7">
         <v>6957</v>
@@ -1500,7 +1491,7 @@
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>11.292</v>
+        <v>11.307</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
@@ -1519,25 +1510,25 @@
         <v>3147</v>
       </c>
       <c r="D28" s="14">
-        <v>14747</v>
+        <v>14746</v>
       </c>
       <c r="E28" s="14">
-        <v>14349</v>
+        <v>14348</v>
       </c>
       <c r="F28" s="14">
         <v>8842</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>14.747</v>
+        <v>14.746</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>14.349</v>
+        <v>14.348000000000001</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.6678353313729926</v>
+        <v>1.6677222347885094</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1546,31 +1537,31 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>51.45</v>
+        <v>109.74</v>
       </c>
       <c r="C29" s="6">
-        <v>3530</v>
+        <v>5134</v>
       </c>
       <c r="D29" s="7">
-        <v>14709</v>
+        <v>14708</v>
       </c>
       <c r="E29" s="7">
-        <v>14709</v>
+        <v>13783</v>
       </c>
       <c r="F29" s="7">
-        <v>9210</v>
+        <v>10367</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>14.709</v>
+        <v>14.708</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>14.709</v>
+        <v>13.782999999999999</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.5970684039087948</v>
+        <v>1.4187325166393363</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1579,19 +1570,19 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>109.74</v>
+        <v>51.45</v>
       </c>
       <c r="C30" s="13">
-        <v>5134</v>
+        <v>3530</v>
       </c>
       <c r="D30" s="14">
         <v>14708</v>
       </c>
       <c r="E30" s="14">
-        <v>13783</v>
+        <v>14708</v>
       </c>
       <c r="F30" s="14">
-        <v>10367</v>
+        <v>9210</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
@@ -1599,11 +1590,11 @@
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>13.782999999999999</v>
+        <v>14.708</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.4187325166393363</v>
+        <v>1.5969598262757871</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1717,25 +1708,25 @@
         <v>2739</v>
       </c>
       <c r="D34" s="14">
-        <v>14463</v>
+        <v>14473</v>
       </c>
       <c r="E34" s="14">
-        <v>13923</v>
+        <v>13933</v>
       </c>
       <c r="F34" s="14">
         <v>7775</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>14.462999999999999</v>
+        <v>14.473000000000001</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>13.923</v>
+        <v>13.933</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.8601929260450161</v>
+        <v>1.8614790996784565</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1783,25 +1774,25 @@
         <v>5093</v>
       </c>
       <c r="D36" s="14">
-        <v>13645</v>
+        <v>13655</v>
       </c>
       <c r="E36" s="14">
-        <v>12352</v>
+        <v>12362</v>
       </c>
       <c r="F36" s="14">
         <v>7977</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>13.645</v>
+        <v>13.654999999999999</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>12.352</v>
+        <v>12.362</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.7105428105804188</v>
+        <v>1.7117964146922402</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1816,25 +1807,25 @@
         <v>3411</v>
       </c>
       <c r="D37" s="7">
-        <v>13645</v>
+        <v>13655</v>
       </c>
       <c r="E37" s="7">
-        <v>12323</v>
+        <v>12333</v>
       </c>
       <c r="F37" s="7">
         <v>7991</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" si="0"/>
-        <v>13.645</v>
+        <v>13.654999999999999</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="1"/>
-        <v>12.323</v>
+        <v>12.333</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" si="2"/>
-        <v>1.7075459892378926</v>
+        <v>1.7087973970717056</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1922,7 +1913,7 @@
       </c>
       <c r="I41" s="22">
         <f>IFERROR(AVERAGE(I5:I39),"")</f>
-        <v>1.8329912833197421</v>
+        <v>1.8331115924336632</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CD597F-945E-47A1-ABB6-C5B0CC9024A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07D25B5-6C3C-483B-BE91-AFD614DD4466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -265,49 +265,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07D25B5-6C3C-483B-BE91-AFD614DD4466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FC8234-542F-4231-B491-974949A70A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -144,37 +144,37 @@
     <t>T-09A</t>
   </si>
   <si>
+    <t>T-09B</t>
+  </si>
+  <si>
+    <t>T-06C</t>
+  </si>
+  <si>
+    <t>T-03B</t>
+  </si>
+  <si>
+    <t>T-03A</t>
+  </si>
+  <si>
+    <t>T-08A</t>
+  </si>
+  <si>
+    <t>T-01</t>
+  </si>
+  <si>
+    <t>T-04A</t>
+  </si>
+  <si>
+    <t>T-04B</t>
+  </si>
+  <si>
     <t>T-01A</t>
   </si>
   <si>
-    <t>T-09B</t>
-  </si>
-  <si>
-    <t>T-03A</t>
-  </si>
-  <si>
-    <t>T-03B</t>
-  </si>
-  <si>
-    <t>T-01</t>
-  </si>
-  <si>
-    <t>T-06C</t>
-  </si>
-  <si>
-    <t>T-08A</t>
-  </si>
-  <si>
-    <t>T-04A</t>
-  </si>
-  <si>
-    <t>T-04B</t>
+    <t>T-04</t>
   </si>
   <si>
     <t>T-02</t>
-  </si>
-  <si>
-    <t>T-04</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -760,25 +760,25 @@
         <v>3271</v>
       </c>
       <c r="D5" s="7">
-        <v>23838</v>
+        <v>26358</v>
       </c>
       <c r="E5" s="7">
-        <v>22737</v>
+        <v>25257</v>
       </c>
       <c r="F5" s="7">
         <v>11475</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G39" si="0">D5/1000</f>
-        <v>23.838000000000001</v>
+        <v>26.358000000000001</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H39" si="1">E5/1000</f>
-        <v>22.736999999999998</v>
+        <v>25.257000000000001</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I39" si="2">IFERROR(D5/F5,"")</f>
-        <v>2.0773856209150328</v>
+        <v>2.2969934640522878</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -793,25 +793,25 @@
         <v>2992</v>
       </c>
       <c r="D6" s="14">
-        <v>23623</v>
+        <v>26143</v>
       </c>
       <c r="E6" s="14">
-        <v>22003</v>
+        <v>24522</v>
       </c>
       <c r="F6" s="14">
         <v>11982</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>23.623000000000001</v>
+        <v>26.143000000000001</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>22.003</v>
+        <v>24.521999999999998</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>1.9715406442997829</v>
+        <v>2.1818561175095978</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -826,25 +826,25 @@
         <v>3110</v>
       </c>
       <c r="D7" s="7">
-        <v>22053</v>
+        <v>24573</v>
       </c>
       <c r="E7" s="7">
-        <v>21040</v>
+        <v>23560</v>
       </c>
       <c r="F7" s="7">
         <v>11159</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>22.053000000000001</v>
+        <v>24.573</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>21.04</v>
+        <v>23.56</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>1.9762523523613227</v>
+        <v>2.2020790393404428</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -859,25 +859,25 @@
         <v>3078</v>
       </c>
       <c r="D8" s="14">
-        <v>21383</v>
+        <v>23903</v>
       </c>
       <c r="E8" s="14">
-        <v>20791</v>
+        <v>23310</v>
       </c>
       <c r="F8" s="14">
         <v>11323</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>21.382999999999999</v>
+        <v>23.902999999999999</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>20.791</v>
+        <v>23.31</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>1.8884571226706703</v>
+        <v>2.1110129824251525</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -892,25 +892,25 @@
         <v>3100</v>
       </c>
       <c r="D9" s="7">
-        <v>21080</v>
+        <v>23600</v>
       </c>
       <c r="E9" s="7">
-        <v>19729</v>
+        <v>22249</v>
       </c>
       <c r="F9" s="7">
         <v>10871</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>21.08</v>
+        <v>23.6</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>19.728999999999999</v>
+        <v>22.248999999999999</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>1.9391040382669487</v>
+        <v>2.1709134394259957</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -925,25 +925,25 @@
         <v>3161</v>
       </c>
       <c r="D10" s="14">
-        <v>21039</v>
+        <v>23559</v>
       </c>
       <c r="E10" s="14">
-        <v>19723</v>
+        <v>22243</v>
       </c>
       <c r="F10" s="14">
         <v>11726</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>21.039000000000001</v>
+        <v>23.559000000000001</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>19.722999999999999</v>
+        <v>22.242999999999999</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>1.7942179771448064</v>
+        <v>2.0091250213201435</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -958,25 +958,25 @@
         <v>3481</v>
       </c>
       <c r="D11" s="7">
-        <v>20821</v>
+        <v>23341</v>
       </c>
       <c r="E11" s="7">
-        <v>18998</v>
+        <v>21518</v>
       </c>
       <c r="F11" s="7">
         <v>10886</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>20.821000000000002</v>
+        <v>23.341000000000001</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>18.998000000000001</v>
+        <v>21.518000000000001</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>1.9126400881866619</v>
+        <v>2.1441300753261068</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -991,25 +991,25 @@
         <v>3197</v>
       </c>
       <c r="D12" s="14">
-        <v>20599</v>
+        <v>23118</v>
       </c>
       <c r="E12" s="14">
-        <v>19147</v>
+        <v>21667</v>
       </c>
       <c r="F12" s="14">
         <v>11107</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>20.599</v>
+        <v>23.117999999999999</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>19.146999999999998</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>1.8545962005942198</v>
+        <v>2.0813901143423066</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1024,25 +1024,25 @@
         <v>4140</v>
       </c>
       <c r="D13" s="7">
-        <v>19773</v>
+        <v>22293</v>
       </c>
       <c r="E13" s="7">
-        <v>17939</v>
+        <v>20458</v>
       </c>
       <c r="F13" s="7">
         <v>10009</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>19.773</v>
+        <v>22.292999999999999</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>17.939</v>
+        <v>20.457999999999998</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>1.9755220301728444</v>
+        <v>2.2272954341093016</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1057,25 +1057,25 @@
         <v>6934</v>
       </c>
       <c r="D14" s="14">
-        <v>19230</v>
+        <v>21750</v>
       </c>
       <c r="E14" s="14">
-        <v>17330</v>
+        <v>19850</v>
       </c>
       <c r="F14" s="14">
         <v>9384</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>19.23</v>
+        <v>21.75</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>17.329999999999998</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>2.0492327365728902</v>
+        <v>2.3177749360613809</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1090,25 +1090,25 @@
         <v>5499</v>
       </c>
       <c r="D15" s="7">
-        <v>16882</v>
+        <v>19402</v>
       </c>
       <c r="E15" s="7">
-        <v>15960</v>
+        <v>18479</v>
       </c>
       <c r="F15" s="7">
         <v>8307</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>16.882000000000001</v>
+        <v>19.402000000000001</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>15.96</v>
+        <v>18.478999999999999</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>2.0322619477549053</v>
+        <v>2.3356205609726737</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1123,25 +1123,25 @@
         <v>4455</v>
       </c>
       <c r="D16" s="14">
-        <v>16882</v>
+        <v>19402</v>
       </c>
       <c r="E16" s="14">
-        <v>14420</v>
+        <v>16939</v>
       </c>
       <c r="F16" s="14">
         <v>7221</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>16.882000000000001</v>
+        <v>19.402000000000001</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>14.42</v>
+        <v>16.939</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>2.3379033374878824</v>
+        <v>2.6868854729261873</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1156,25 +1156,25 @@
         <v>4640</v>
       </c>
       <c r="D17" s="7">
-        <v>16877</v>
+        <v>19397</v>
       </c>
       <c r="E17" s="7">
-        <v>15985</v>
+        <v>18505</v>
       </c>
       <c r="F17" s="7">
         <v>8248</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>16.876999999999999</v>
+        <v>19.396999999999998</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>15.984999999999999</v>
+        <v>18.504999999999999</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>2.046193016488846</v>
+        <v>2.3517216294859358</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1189,25 +1189,25 @@
         <v>4536</v>
       </c>
       <c r="D18" s="14">
-        <v>16877</v>
+        <v>19397</v>
       </c>
       <c r="E18" s="14">
-        <v>15985</v>
+        <v>18505</v>
       </c>
       <c r="F18" s="14">
         <v>8256</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>16.876999999999999</v>
+        <v>19.396999999999998</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>15.984999999999999</v>
+        <v>18.504999999999999</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>2.0442102713178296</v>
+        <v>2.3494428294573644</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1222,25 +1222,25 @@
         <v>3399</v>
       </c>
       <c r="D19" s="7">
-        <v>16083</v>
+        <v>18603</v>
       </c>
       <c r="E19" s="7">
-        <v>15611</v>
+        <v>18131</v>
       </c>
       <c r="F19" s="7">
         <v>9205</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>16.082999999999998</v>
+        <v>18.603000000000002</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>15.611000000000001</v>
+        <v>18.131</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>1.7472026072786528</v>
+        <v>2.020966865833786</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1255,25 +1255,25 @@
         <v>3108</v>
       </c>
       <c r="D20" s="14">
-        <v>16083</v>
+        <v>18603</v>
       </c>
       <c r="E20" s="14">
-        <v>15582</v>
+        <v>18102</v>
       </c>
       <c r="F20" s="14">
         <v>8461</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>16.082999999999998</v>
+        <v>18.603000000000002</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>15.582000000000001</v>
+        <v>18.102</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>1.9008391443091832</v>
+        <v>2.198676279399598</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1288,25 +1288,25 @@
         <v>3736</v>
       </c>
       <c r="D21" s="7">
-        <v>15664</v>
+        <v>18184</v>
       </c>
       <c r="E21" s="7">
-        <v>14658</v>
+        <v>17178</v>
       </c>
       <c r="F21" s="7">
         <v>9056</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>15.664</v>
+        <v>18.184000000000001</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>14.657999999999999</v>
+        <v>17.178000000000001</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>1.7296819787985867</v>
+        <v>2.0079505300353357</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1321,25 +1321,25 @@
         <v>3002</v>
       </c>
       <c r="D22" s="14">
-        <v>15611</v>
+        <v>18131</v>
       </c>
       <c r="E22" s="14">
-        <v>13947</v>
+        <v>16467</v>
       </c>
       <c r="F22" s="14">
         <v>8442</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>15.611000000000001</v>
+        <v>18.131</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>13.946999999999999</v>
+        <v>16.466999999999999</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>1.8492063492063493</v>
+        <v>2.1477138118929164</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1354,25 +1354,25 @@
         <v>5085</v>
       </c>
       <c r="D23" s="7">
-        <v>14842</v>
+        <v>17361</v>
       </c>
       <c r="E23" s="7">
-        <v>13279</v>
+        <v>15799</v>
       </c>
       <c r="F23" s="7">
         <v>8501</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>14.842000000000001</v>
+        <v>17.361000000000001</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>13.279</v>
+        <v>15.798999999999999</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>1.7459122456181626</v>
+        <v>2.0422303258440184</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1387,25 +1387,25 @@
         <v>5071</v>
       </c>
       <c r="D24" s="14">
-        <v>14842</v>
+        <v>17361</v>
       </c>
       <c r="E24" s="14">
-        <v>14252</v>
+        <v>16772</v>
       </c>
       <c r="F24" s="14">
         <v>9352</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>14.842000000000001</v>
+        <v>17.361000000000001</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>14.252000000000001</v>
+        <v>16.771999999999998</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.5870402053036783</v>
+        <v>1.8563943541488452</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1420,25 +1420,25 @@
         <v>4134</v>
       </c>
       <c r="D25" s="7">
-        <v>14802</v>
+        <v>17322</v>
       </c>
       <c r="E25" s="7">
-        <v>13207</v>
+        <v>15727</v>
       </c>
       <c r="F25" s="7">
         <v>7712</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>14.802</v>
+        <v>17.321999999999999</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>13.207000000000001</v>
+        <v>15.727</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>1.9193464730290457</v>
+        <v>2.2461099585062239</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1453,25 +1453,25 @@
         <v>5858</v>
       </c>
       <c r="D26" s="14">
-        <v>14802</v>
+        <v>17322</v>
       </c>
       <c r="E26" s="14">
-        <v>13207</v>
+        <v>15727</v>
       </c>
       <c r="F26" s="14">
         <v>7712</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>14.802</v>
+        <v>17.321999999999999</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>13.207000000000001</v>
+        <v>15.727</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>1.9193464730290457</v>
+        <v>2.2461099585062239</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1486,25 +1486,25 @@
         <v>6929</v>
       </c>
       <c r="D27" s="7">
-        <v>14802</v>
+        <v>17322</v>
       </c>
       <c r="E27" s="7">
-        <v>11307</v>
+        <v>13827</v>
       </c>
       <c r="F27" s="7">
         <v>6957</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>14.802</v>
+        <v>17.321999999999999</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>11.307</v>
+        <v>13.827</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>2.1276412246658043</v>
+        <v>2.4898663216903838</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1519,25 +1519,25 @@
         <v>3147</v>
       </c>
       <c r="D28" s="14">
-        <v>14746</v>
+        <v>17266</v>
       </c>
       <c r="E28" s="14">
-        <v>14348</v>
+        <v>16868</v>
       </c>
       <c r="F28" s="14">
         <v>8842</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>14.746</v>
+        <v>17.265999999999998</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>14.348000000000001</v>
+        <v>16.867999999999999</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.6677222347885094</v>
+        <v>1.9527256276860439</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1546,31 +1546,31 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>109.74</v>
+        <v>51.45</v>
       </c>
       <c r="C29" s="6">
-        <v>5134</v>
+        <v>3530</v>
       </c>
       <c r="D29" s="7">
-        <v>14708</v>
+        <v>17228</v>
       </c>
       <c r="E29" s="7">
-        <v>13783</v>
+        <v>17228</v>
       </c>
       <c r="F29" s="7">
-        <v>10367</v>
+        <v>9210</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>14.708</v>
+        <v>17.228000000000002</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>13.782999999999999</v>
+        <v>17.228000000000002</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.4187325166393363</v>
+        <v>1.8705754614549404</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1579,31 +1579,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>51.45</v>
+        <v>31.74</v>
       </c>
       <c r="C30" s="13">
-        <v>3530</v>
+        <v>2739</v>
       </c>
       <c r="D30" s="14">
-        <v>14708</v>
+        <v>16993</v>
       </c>
       <c r="E30" s="14">
-        <v>14708</v>
+        <v>16453</v>
       </c>
       <c r="F30" s="14">
-        <v>9210</v>
+        <v>7775</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>14.708</v>
+        <v>16.992999999999999</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>14.708</v>
+        <v>16.452999999999999</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.5969598262757871</v>
+        <v>2.185594855305466</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1612,31 +1612,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>108.06</v>
+        <v>113.04</v>
       </c>
       <c r="C31" s="6">
-        <v>5283</v>
+        <v>5041</v>
       </c>
       <c r="D31" s="7">
-        <v>14601</v>
+        <v>16870</v>
       </c>
       <c r="E31" s="7">
-        <v>13332</v>
+        <v>14233</v>
       </c>
       <c r="F31" s="7">
-        <v>9732</v>
+        <v>8850</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>14.601000000000001</v>
+        <v>16.87</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>13.332000000000001</v>
+        <v>14.233000000000001</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>1.500308261405672</v>
+        <v>1.9062146892655367</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1645,31 +1645,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>113.04</v>
+        <v>108.06</v>
       </c>
       <c r="C32" s="13">
-        <v>5041</v>
+        <v>5283</v>
       </c>
       <c r="D32" s="14">
-        <v>14601</v>
+        <v>16832</v>
       </c>
       <c r="E32" s="14">
-        <v>12353</v>
+        <v>15212</v>
       </c>
       <c r="F32" s="14">
-        <v>8850</v>
+        <v>9732</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>14.601000000000001</v>
+        <v>16.832000000000001</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>12.353</v>
+        <v>15.212</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>1.6498305084745764</v>
+        <v>1.7295519934237567</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1678,31 +1678,31 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>110.23</v>
+        <v>14.18</v>
       </c>
       <c r="C33" s="6">
-        <v>5065</v>
+        <v>1756</v>
       </c>
       <c r="D33" s="7">
-        <v>14572</v>
+        <v>16654</v>
       </c>
       <c r="E33" s="7">
-        <v>12412</v>
+        <v>15919</v>
       </c>
       <c r="F33" s="7">
-        <v>9477</v>
+        <v>7912</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>14.571999999999999</v>
+        <v>16.654</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>12.412000000000001</v>
+        <v>15.919</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.5376173894692413</v>
+        <v>2.1049039433771486</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1711,31 +1711,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>31.74</v>
+        <v>110.23</v>
       </c>
       <c r="C34" s="13">
-        <v>2739</v>
+        <v>5065</v>
       </c>
       <c r="D34" s="14">
-        <v>14473</v>
+        <v>16451</v>
       </c>
       <c r="E34" s="14">
-        <v>13933</v>
+        <v>12673</v>
       </c>
       <c r="F34" s="14">
-        <v>7775</v>
+        <v>9477</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>14.473000000000001</v>
+        <v>16.451000000000001</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>13.933</v>
+        <v>12.673</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.8614790996784565</v>
+        <v>1.7358868840350321</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1744,31 +1744,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>14.18</v>
+        <v>100.42</v>
       </c>
       <c r="C35" s="6">
-        <v>1756</v>
+        <v>5093</v>
       </c>
       <c r="D35" s="7">
-        <v>14134</v>
+        <v>15902</v>
       </c>
       <c r="E35" s="7">
-        <v>13399</v>
+        <v>14319</v>
       </c>
       <c r="F35" s="7">
-        <v>7912</v>
+        <v>7977</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>14.134</v>
+        <v>15.901999999999999</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>13.398999999999999</v>
+        <v>14.319000000000001</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>1.7864004044489383</v>
+        <v>1.9934812586185282</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1777,31 +1777,31 @@
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>100.42</v>
+        <v>51.93</v>
       </c>
       <c r="C36" s="13">
-        <v>5093</v>
+        <v>3411</v>
       </c>
       <c r="D36" s="14">
-        <v>13655</v>
+        <v>15902</v>
       </c>
       <c r="E36" s="14">
-        <v>12362</v>
+        <v>14853</v>
       </c>
       <c r="F36" s="14">
-        <v>7977</v>
+        <v>7991</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>13.654999999999999</v>
+        <v>15.901999999999999</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>12.362</v>
+        <v>14.853</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.7117964146922402</v>
+        <v>1.9899887373294958</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1810,31 +1810,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>51.93</v>
+        <v>109.74</v>
       </c>
       <c r="C37" s="6">
-        <v>3411</v>
+        <v>5134</v>
       </c>
       <c r="D37" s="7">
-        <v>13655</v>
+        <v>14709</v>
       </c>
       <c r="E37" s="7">
-        <v>12333</v>
+        <v>13783</v>
       </c>
       <c r="F37" s="7">
-        <v>7991</v>
+        <v>10367</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" si="0"/>
-        <v>13.654999999999999</v>
+        <v>14.709</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="1"/>
-        <v>12.333</v>
+        <v>13.782999999999999</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" si="2"/>
-        <v>1.7087973970717056</v>
+        <v>1.4188289765602393</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1843,31 +1843,31 @@
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>210.74</v>
+        <v>107.45</v>
       </c>
       <c r="C38" s="13">
-        <v>9468</v>
+        <v>5565</v>
       </c>
       <c r="D38" s="14">
-        <v>12696</v>
+        <v>13305</v>
       </c>
       <c r="E38" s="14">
-        <v>10412</v>
+        <v>12189</v>
       </c>
       <c r="F38" s="14">
-        <v>7561</v>
+        <v>7077</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="0"/>
-        <v>12.696</v>
+        <v>13.305</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="1"/>
-        <v>10.412000000000001</v>
+        <v>12.189</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="2"/>
-        <v>1.6791429705065468</v>
+        <v>1.8800339126748622</v>
       </c>
       <c r="J38" s="17"/>
     </row>
@@ -1876,31 +1876,31 @@
         <v>46</v>
       </c>
       <c r="B39" s="5">
-        <v>107.45</v>
+        <v>210.74</v>
       </c>
       <c r="C39" s="6">
-        <v>5565</v>
+        <v>9468</v>
       </c>
       <c r="D39" s="7">
-        <v>11425</v>
+        <v>12697</v>
       </c>
       <c r="E39" s="7">
-        <v>10040</v>
+        <v>10661</v>
       </c>
       <c r="F39" s="7">
-        <v>7077</v>
+        <v>7561</v>
       </c>
       <c r="G39" s="8">
         <f t="shared" si="0"/>
-        <v>11.425000000000001</v>
+        <v>12.696999999999999</v>
       </c>
       <c r="H39" s="8">
         <f t="shared" si="1"/>
-        <v>10.039999999999999</v>
+        <v>10.661</v>
       </c>
       <c r="I39" s="9">
         <f t="shared" si="2"/>
-        <v>1.6143846262540624</v>
+        <v>1.6792752281444254</v>
       </c>
       <c r="J39" s="10"/>
     </row>
@@ -1914,15 +1914,15 @@
       </c>
       <c r="D41" s="20">
         <f>MAX(D5:D39)</f>
-        <v>23838</v>
+        <v>26358</v>
       </c>
       <c r="G41" s="21">
         <f>IFERROR(MAX(G5:G39),"")</f>
-        <v>23.838000000000001</v>
+        <v>26.358000000000001</v>
       </c>
       <c r="I41" s="22">
         <f>IFERROR(AVERAGE(I5:I39),"")</f>
-        <v>1.8331115924336632</v>
+        <v>2.0905520311567907</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_JAVA_distancias.xlsx
+++ b/FAZENDA_JAVA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FC8234-542F-4231-B491-974949A70A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A89454-09FF-466D-9594-2B7A7A103AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -265,58 +265,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
